--- a/data/Type1/species by biomass/ES_Cantabrian_NIA_Station_3.xlsx
+++ b/data/Type1/species by biomass/ES_Cantabrian_NIA_Station_3.xlsx
@@ -1,33 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Dropbox\0_IEO\Ciencia\ICES\WKBENTH4\5_OUTPUTS\Type_1\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC9656E-13C1-4C56-B5FE-C3ECBA51CB90}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Metadata and protocols" sheetId="1" r:id="rId1"/>
-    <sheet name="Species information" sheetId="3" r:id="rId2"/>
-    <sheet name="Time series information" sheetId="4" r:id="rId3"/>
+    <sheet name="Metadata and protocols" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Time series information" sheetId="4" state="visible" r:id="rId3"/>
+    <sheet name="Species information" sheetId="3" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0" refMode="R1C1"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
   <si>
     <t>cl_name</t>
   </si>
@@ -297,23 +285,212 @@
   </si>
   <si>
     <t>2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type_2_year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">station_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">longitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">latitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">depth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">area_sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replicates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">substrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assessment_unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_abundance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_biomass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">richness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rel Margalef div (dens)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rel Margalef div (biom)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SoS_2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">area_sampled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_number_individuals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total_biomass_correct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rel.margalef.div.(dens)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rel.margalef.div.(biom)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_BQI_2009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_3.xlsx_2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_3_2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_Station_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">387.8658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">otter_trawl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upper bathyal sediment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_3.xlsx_2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_3_2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_3.xlsx_2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_3_2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420.2323303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_3.xlsx_2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_3_2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_3.xlsx_2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_3_2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_3.xlsx_2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_3_2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.5970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_3.xlsx_2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_3_2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_3.xlsx_2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_3_2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_3.xlsx_2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_3_2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_3.xlsx_2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_3_2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -339,9 +516,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -637,11 +813,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -649,7 +825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -657,7 +833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -665,7 +841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -673,7 +849,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -681,7 +857,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -689,7 +865,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -697,7 +873,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -705,7 +881,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -713,7 +889,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -721,7 +897,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -729,7 +905,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -737,7 +913,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -745,7 +921,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -753,7 +929,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -761,7 +937,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -769,7 +945,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -777,7 +953,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -785,7 +961,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -793,7 +969,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -801,7 +977,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -809,7 +985,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -817,7 +993,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -832,11 +1008,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I185"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -865,26 +1041,26 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>40</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>2013</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>29</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>100930</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>9.2712397609999995E-5</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>5.5627438569999998E-4</v>
       </c>
       <c r="H2" t="s">
@@ -894,26 +1070,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>40</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>2013</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="s">
         <v>29</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>100946</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>7.4169918089999994E-5</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>3.708495905E-4</v>
       </c>
       <c r="H3" t="s">
@@ -923,26 +1099,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>40</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>2013</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="s">
         <v>29</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>107120</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>3.7084959049999998E-5</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>1.2979735670000001E-4</v>
       </c>
       <c r="H4" t="s">
@@ -952,26 +1128,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>40</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>2013</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="s">
         <v>29</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>107230</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>1.2979735670000001E-4</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>5.5627438569999998E-4</v>
       </c>
       <c r="H5" t="s">
@@ -981,26 +1157,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>40</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>2013</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="s">
         <v>29</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>107236</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>5.5627438569999999E-5</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>5.0064694709999998E-4</v>
       </c>
       <c r="H6" t="s">
@@ -1010,26 +1186,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>40</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>2013</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>107239</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>3.7084959049999998E-5</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>7.4169918089999994E-5</v>
       </c>
       <c r="H7" t="s">
@@ -1039,26 +1215,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>40</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>2013</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>107254</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>1.2979735670000001E-4</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>1.214532409E-2</v>
       </c>
       <c r="H8" t="s">
@@ -1068,26 +1244,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>40</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>2013</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>107292</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>1.2979735670000001E-4</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>9.2712397609999995E-5</v>
       </c>
       <c r="H9" t="s">
@@ -1097,26 +1273,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>40</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>2013</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>107342</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>1.8542479520000001E-5</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>1.8542479520000001E-5</v>
       </c>
       <c r="H10" t="s">
@@ -1126,26 +1302,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>40</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>2013</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>107558</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>7.4169918089999994E-5</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>1.8542479520000001E-5</v>
       </c>
       <c r="H11" t="s">
@@ -1155,26 +1331,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>40</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>2013</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="s">
         <v>29</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>107642</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>1.8542479520000001E-5</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>3.7084959049999998E-5</v>
       </c>
       <c r="H12" t="s">
@@ -1184,26 +1360,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>40</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>2013</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="s">
         <v>29</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>107643</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>2.5959471329999999E-4</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>1.0940062919999999E-3</v>
       </c>
       <c r="H13" t="s">
@@ -1213,26 +1389,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>40</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>2013</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="s">
         <v>29</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>107661</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>7.6024166040000003E-4</v>
       </c>
-      <c r="G14">
+      <c r="G14" t="n">
         <v>3.0595091210000001E-3</v>
       </c>
       <c r="H14" t="s">
@@ -1242,26 +1418,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>40</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>2013</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="s">
         <v>29</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>107677</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>2.5774046540000001E-3</v>
       </c>
-      <c r="G15">
+      <c r="G15" t="n">
         <v>3.523071109E-3</v>
       </c>
       <c r="H15" t="s">
@@ -1271,26 +1447,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>40</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>2013</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="s">
         <v>29</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>107696</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>9.2712397609999995E-5</v>
       </c>
-      <c r="G16">
+      <c r="G16" t="n">
         <v>4.4501950849999998E-4</v>
       </c>
       <c r="H16" t="s">
@@ -1300,26 +1476,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>40</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="n">
         <v>2013</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="s">
         <v>29</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>117302</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>1.8542479520000001E-5</v>
       </c>
-      <c r="G17">
+      <c r="G17" t="n">
         <v>1.8542479520000001E-5</v>
       </c>
       <c r="H17" t="s">
@@ -1329,26 +1505,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>40</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="n">
         <v>2013</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="s">
         <v>29</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>124257</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>3.7084959049999998E-5</v>
       </c>
-      <c r="G18">
+      <c r="G18" t="n">
         <v>1.9469603500000001E-3</v>
       </c>
       <c r="H18" t="s">
@@ -1358,26 +1534,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>40</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="n">
         <v>2013</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="s">
         <v>29</v>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>124535</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="n">
         <v>3.7084959049999998E-5</v>
       </c>
-      <c r="G19">
+      <c r="G19" t="n">
         <v>5.4700314589999997E-3</v>
       </c>
       <c r="H19" t="s">
@@ -1387,26 +1563,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>40</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="n">
         <v>2013</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="s">
         <v>29</v>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>124951</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="n">
         <v>1.8542479520000001E-5</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>7.4169918089999994E-5</v>
       </c>
       <c r="H20" t="s">
@@ -1416,26 +1592,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>40</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="n">
         <v>2013</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="s">
         <v>29</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>125371</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>1.8542479520000001E-5</v>
       </c>
-      <c r="G21">
+      <c r="G21" t="n">
         <v>5.5627438569999999E-5</v>
       </c>
       <c r="H21" t="s">
@@ -1445,26 +1621,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>40</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="n">
         <v>2013</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="s">
         <v>29</v>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>128506</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>3.7084959049999998E-5</v>
       </c>
-      <c r="G22">
+      <c r="G22" t="n">
         <v>2.225097543E-4</v>
       </c>
       <c r="H22" t="s">
@@ -1474,26 +1650,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>40</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="n">
         <v>2013</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="s">
         <v>29</v>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>132511</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>1.8542479520000001E-5</v>
       </c>
-      <c r="G23">
+      <c r="G23" t="n">
         <v>2.781371928E-4</v>
       </c>
       <c r="H23" t="s">
@@ -1503,26 +1679,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
         <v>40</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="n">
         <v>2013</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="s">
         <v>29</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>138899</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>1.8542479520000001E-5</v>
       </c>
-      <c r="G24">
+      <c r="G24" t="n">
         <v>2.0396727469999999E-4</v>
       </c>
       <c r="H24" t="s">
@@ -1532,26 +1708,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" t="s">
         <v>40</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="n">
         <v>2013</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="s">
         <v>29</v>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>141115</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>1.8542479520000001E-5</v>
       </c>
-      <c r="G25">
+      <c r="G25" t="n">
         <v>4.9137570729999996E-3</v>
       </c>
       <c r="H25" t="s">
@@ -1561,26 +1737,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" t="s">
         <v>40</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="n">
         <v>2013</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="s">
         <v>29</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>149898</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>1.8542479520000001E-5</v>
       </c>
-      <c r="G26">
+      <c r="G26" t="n">
         <v>1.0198363739999999E-3</v>
       </c>
       <c r="H26" t="s">
@@ -1590,26 +1766,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" t="s">
         <v>40</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="n">
         <v>2013</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="s">
         <v>29</v>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>381759</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>1.8542479520000001E-5</v>
       </c>
-      <c r="G27">
+      <c r="G27" t="n">
         <v>2.9667967239999999E-4</v>
       </c>
       <c r="H27" t="s">
@@ -1619,26 +1795,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" t="s">
         <v>40</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="n">
         <v>2013</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="s">
         <v>29</v>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>532031</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>5.5627438569999999E-5</v>
       </c>
-      <c r="G28">
+      <c r="G28" t="n">
         <v>1.3906859640000001E-3</v>
       </c>
       <c r="H28" t="s">
@@ -1648,26 +1824,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>40</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="n">
         <v>2014</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="s">
         <v>29</v>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>100930</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>2.1962602079999999E-4</v>
       </c>
-      <c r="G29">
+      <c r="G29" t="n">
         <v>5.6503785350000002E-3</v>
       </c>
       <c r="H29" t="s">
@@ -1677,26 +1853,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" t="s">
         <v>40</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="n">
         <v>2014</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="s">
         <v>29</v>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>107120</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="n">
         <v>1.9966001889999999E-5</v>
       </c>
-      <c r="G30">
+      <c r="G30" t="n">
         <v>1.9966001889999999E-5</v>
       </c>
       <c r="H30" t="s">
@@ -1706,26 +1882,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" t="s">
         <v>40</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="n">
         <v>2014</v>
       </c>
-      <c r="C31">
+      <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="s">
         <v>29</v>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>107230</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="n">
         <v>3.194560303E-4</v>
       </c>
-      <c r="G31">
+      <c r="G31" t="n">
         <v>8.9847008510000003E-4</v>
       </c>
       <c r="H31" t="s">
@@ -1735,26 +1911,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="n">
         <v>2014</v>
       </c>
-      <c r="C32">
+      <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="s">
         <v>29</v>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>107239</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="n">
         <v>1.9966001889999999E-5</v>
       </c>
-      <c r="G32">
+      <c r="G32" t="n">
         <v>3.9932003779999998E-5</v>
       </c>
       <c r="H32" t="s">
@@ -1764,26 +1940,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" t="s">
         <v>40</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="n">
         <v>2014</v>
       </c>
-      <c r="C33">
+      <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>107254</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="n">
         <v>6.9881006620000003E-4</v>
       </c>
-      <c r="G33">
+      <c r="G33" t="n">
         <v>7.3175396929999997E-2</v>
       </c>
       <c r="H33" t="s">
@@ -1793,26 +1969,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" t="s">
         <v>40</v>
       </c>
-      <c r="B34">
+      <c r="B34" t="n">
         <v>2014</v>
       </c>
-      <c r="C34">
+      <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="s">
         <v>29</v>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>107292</v>
       </c>
-      <c r="F34">
+      <c r="F34" t="n">
         <v>9.9830009460000001E-5</v>
       </c>
-      <c r="G34">
+      <c r="G34" t="n">
         <v>9.9830009460000001E-5</v>
       </c>
       <c r="H34" t="s">
@@ -1822,26 +1998,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35" t="s">
         <v>40</v>
       </c>
-      <c r="B35">
+      <c r="B35" t="n">
         <v>2014</v>
       </c>
-      <c r="C35">
+      <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="s">
         <v>29</v>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>107342</v>
       </c>
-      <c r="F35">
+      <c r="F35" t="n">
         <v>9.9830009460000001E-5</v>
       </c>
-      <c r="G35">
+      <c r="G35" t="n">
         <v>2.9949002839999998E-4</v>
       </c>
       <c r="H35" t="s">
@@ -1851,26 +2027,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36" t="s">
         <v>40</v>
       </c>
-      <c r="B36">
+      <c r="B36" t="n">
         <v>2014</v>
       </c>
-      <c r="C36">
+      <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="s">
         <v>29</v>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>107558</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="n">
         <v>1.996600189E-4</v>
       </c>
-      <c r="G36">
+      <c r="G36" t="n">
         <v>5.9898005679999997E-5</v>
       </c>
       <c r="H36" t="s">
@@ -1880,26 +2056,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" t="s">
         <v>40</v>
       </c>
-      <c r="B37">
+      <c r="B37" t="n">
         <v>2014</v>
       </c>
-      <c r="C37">
+      <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="s">
         <v>29</v>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>107564</v>
       </c>
-      <c r="F37">
+      <c r="F37" t="n">
         <v>3.9932003779999998E-5</v>
       </c>
-      <c r="G37">
+      <c r="G37" t="n">
         <v>3.9932003779999998E-5</v>
       </c>
       <c r="H37" t="s">
@@ -1909,26 +2085,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38" t="s">
         <v>40</v>
       </c>
-      <c r="B38">
+      <c r="B38" t="n">
         <v>2014</v>
       </c>
-      <c r="C38">
+      <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="s">
         <v>29</v>
       </c>
-      <c r="E38">
+      <c r="E38" t="n">
         <v>107643</v>
       </c>
-      <c r="F38">
+      <c r="F38" t="n">
         <v>3.9932003779999999E-4</v>
       </c>
-      <c r="G38">
+      <c r="G38" t="n">
         <v>1.5773141490000001E-3</v>
       </c>
       <c r="H38" t="s">
@@ -1938,26 +2114,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39" t="s">
         <v>40</v>
       </c>
-      <c r="B39">
+      <c r="B39" t="n">
         <v>2014</v>
       </c>
-      <c r="C39">
+      <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="s">
         <v>29</v>
       </c>
-      <c r="E39">
+      <c r="E39" t="n">
         <v>107677</v>
       </c>
-      <c r="F39">
+      <c r="F39" t="n">
         <v>1.996600189E-4</v>
       </c>
-      <c r="G39">
+      <c r="G39" t="n">
         <v>1.5972801510000001E-4</v>
       </c>
       <c r="H39" t="s">
@@ -1967,26 +2143,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40" t="s">
         <v>40</v>
       </c>
-      <c r="B40">
+      <c r="B40" t="n">
         <v>2014</v>
       </c>
-      <c r="C40">
+      <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="s">
         <v>29</v>
       </c>
-      <c r="E40">
+      <c r="E40" t="n">
         <v>107696</v>
       </c>
-      <c r="F40">
+      <c r="F40" t="n">
         <v>3.9932003779999998E-5</v>
       </c>
-      <c r="G40">
+      <c r="G40" t="n">
         <v>3.194560303E-4</v>
       </c>
       <c r="H40" t="s">
@@ -1996,26 +2172,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" t="s">
         <v>40</v>
       </c>
-      <c r="B41">
+      <c r="B41" t="n">
         <v>2014</v>
       </c>
-      <c r="C41">
+      <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="s">
         <v>29</v>
       </c>
-      <c r="E41">
+      <c r="E41" t="n">
         <v>123867</v>
       </c>
-      <c r="F41">
+      <c r="F41" t="n">
         <v>1.9966001889999999E-5</v>
       </c>
-      <c r="G41">
+      <c r="G41" t="n">
         <v>2.3959202270000001E-4</v>
       </c>
       <c r="H41" t="s">
@@ -2025,26 +2201,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42" t="s">
         <v>40</v>
       </c>
-      <c r="B42">
+      <c r="B42" t="n">
         <v>2014</v>
       </c>
-      <c r="C42">
+      <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="s">
         <v>29</v>
       </c>
-      <c r="E42">
+      <c r="E42" t="n">
         <v>124224</v>
       </c>
-      <c r="F42">
+      <c r="F42" t="n">
         <v>9.9830009460000007E-4</v>
       </c>
-      <c r="G42">
+      <c r="G42" t="n">
         <v>5.3908205109999996E-4</v>
       </c>
       <c r="H42" t="s">
@@ -2054,26 +2230,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43" t="s">
         <v>40</v>
       </c>
-      <c r="B43">
+      <c r="B43" t="n">
         <v>2014</v>
       </c>
-      <c r="C43">
+      <c r="C43" t="n">
         <v>1</v>
       </c>
       <c r="D43" t="s">
         <v>29</v>
       </c>
-      <c r="E43">
+      <c r="E43" t="n">
         <v>124535</v>
       </c>
-      <c r="F43">
+      <c r="F43" t="n">
         <v>1.9966001889999999E-5</v>
       </c>
-      <c r="G43">
+      <c r="G43" t="n">
         <v>2.8551382709999999E-3</v>
       </c>
       <c r="H43" t="s">
@@ -2083,26 +2259,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44" t="s">
         <v>40</v>
       </c>
-      <c r="B44">
+      <c r="B44" t="n">
         <v>2014</v>
       </c>
-      <c r="C44">
+      <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="s">
         <v>29</v>
       </c>
-      <c r="E44">
+      <c r="E44" t="n">
         <v>125131</v>
       </c>
-      <c r="F44">
+      <c r="F44" t="n">
         <v>5.9898005679999997E-5</v>
       </c>
-      <c r="G44">
+      <c r="G44" t="n">
         <v>5.9898005679999997E-5</v>
       </c>
       <c r="H44" t="s">
@@ -2112,26 +2288,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45" t="s">
         <v>40</v>
       </c>
-      <c r="B45">
+      <c r="B45" t="n">
         <v>2014</v>
       </c>
-      <c r="C45">
+      <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" t="s">
         <v>29</v>
       </c>
-      <c r="E45">
+      <c r="E45" t="n">
         <v>132511</v>
       </c>
-      <c r="F45">
+      <c r="F45" t="n">
         <v>3.9932003779999998E-5</v>
       </c>
-      <c r="G45">
+      <c r="G45" t="n">
         <v>7.786740738E-4</v>
       </c>
       <c r="H45" t="s">
@@ -2141,26 +2317,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46" t="s">
         <v>40</v>
       </c>
-      <c r="B46">
+      <c r="B46" t="n">
         <v>2014</v>
       </c>
-      <c r="C46">
+      <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="s">
         <v>29</v>
       </c>
-      <c r="E46">
+      <c r="E46" t="n">
         <v>138899</v>
       </c>
-      <c r="F46">
+      <c r="F46" t="n">
         <v>1.5972801510000001E-4</v>
       </c>
-      <c r="G46">
+      <c r="G46" t="n">
         <v>2.1563282039999999E-3</v>
       </c>
       <c r="H46" t="s">
@@ -2170,26 +2346,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47" t="s">
         <v>40</v>
       </c>
-      <c r="B47">
+      <c r="B47" t="n">
         <v>2014</v>
       </c>
-      <c r="C47">
+      <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="s">
         <v>29</v>
       </c>
-      <c r="E47">
+      <c r="E47" t="n">
         <v>139024</v>
       </c>
-      <c r="F47">
+      <c r="F47" t="n">
         <v>5.9898005679999997E-5</v>
       </c>
-      <c r="G47">
+      <c r="G47" t="n">
         <v>4.272724405E-3</v>
       </c>
       <c r="H47" t="s">
@@ -2199,26 +2375,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="A48" t="s">
         <v>40</v>
       </c>
-      <c r="B48">
+      <c r="B48" t="n">
         <v>2014</v>
       </c>
-      <c r="C48">
+      <c r="C48" t="n">
         <v>1</v>
       </c>
       <c r="D48" t="s">
         <v>29</v>
       </c>
-      <c r="E48">
+      <c r="E48" t="n">
         <v>140529</v>
       </c>
-      <c r="F48">
+      <c r="F48" t="n">
         <v>1.9966001889999999E-5</v>
       </c>
-      <c r="G48">
+      <c r="G48" t="n">
         <v>1.79694017E-4</v>
       </c>
       <c r="H48" t="s">
@@ -2228,26 +2404,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="A49" t="s">
         <v>40</v>
       </c>
-      <c r="B49">
+      <c r="B49" t="n">
         <v>2014</v>
       </c>
-      <c r="C49">
+      <c r="C49" t="n">
         <v>1</v>
       </c>
       <c r="D49" t="s">
         <v>29</v>
       </c>
-      <c r="E49">
+      <c r="E49" t="n">
         <v>532031</v>
       </c>
-      <c r="F49">
+      <c r="F49" t="n">
         <v>7.9864007569999999E-5</v>
       </c>
-      <c r="G49">
+      <c r="G49" t="n">
         <v>2.6355122499999999E-3</v>
       </c>
       <c r="H49" t="s">
@@ -2257,26 +2433,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50" t="s">
         <v>40</v>
       </c>
-      <c r="B50">
+      <c r="B50" t="n">
         <v>2015</v>
       </c>
-      <c r="C50">
+      <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" t="s">
         <v>29</v>
       </c>
-      <c r="E50">
+      <c r="E50" t="n">
         <v>100930</v>
       </c>
-      <c r="F50">
+      <c r="F50" t="n">
         <v>1.999981818E-4</v>
       </c>
-      <c r="G50">
+      <c r="G50" t="n">
         <v>2.654521323E-3</v>
       </c>
       <c r="H50" t="s">
@@ -2286,26 +2462,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="A51" t="s">
         <v>40</v>
       </c>
-      <c r="B51">
+      <c r="B51" t="n">
         <v>2015</v>
       </c>
-      <c r="C51">
+      <c r="C51" t="n">
         <v>1</v>
       </c>
       <c r="D51" t="s">
         <v>29</v>
       </c>
-      <c r="E51">
+      <c r="E51" t="n">
         <v>100946</v>
       </c>
-      <c r="F51">
+      <c r="F51" t="n">
         <v>1.8181652889999999E-5</v>
       </c>
-      <c r="G51">
+      <c r="G51" t="n">
         <v>5.454495868E-5</v>
       </c>
       <c r="H51" t="s">
@@ -2315,26 +2491,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="A52" t="s">
         <v>40</v>
       </c>
-      <c r="B52">
+      <c r="B52" t="n">
         <v>2015</v>
       </c>
-      <c r="C52">
+      <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="s">
         <v>29</v>
       </c>
-      <c r="E52">
+      <c r="E52" t="n">
         <v>107120</v>
       </c>
-      <c r="F52">
+      <c r="F52" t="n">
         <v>3.6363305790000001E-5</v>
       </c>
-      <c r="G52">
+      <c r="G52" t="n">
         <v>9.0908264469999995E-5</v>
       </c>
       <c r="H52" t="s">
@@ -2344,26 +2520,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="A53" t="s">
         <v>40</v>
       </c>
-      <c r="B53">
+      <c r="B53" t="n">
         <v>2015</v>
       </c>
-      <c r="C53">
+      <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="s">
         <v>29</v>
       </c>
-      <c r="E53">
+      <c r="E53" t="n">
         <v>107230</v>
       </c>
-      <c r="F53">
+      <c r="F53" t="n">
         <v>5.454495868E-5</v>
       </c>
-      <c r="G53">
+      <c r="G53" t="n">
         <v>5.454495868E-5</v>
       </c>
       <c r="H53" t="s">
@@ -2373,26 +2549,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="A54" t="s">
         <v>40</v>
       </c>
-      <c r="B54">
+      <c r="B54" t="n">
         <v>2015</v>
       </c>
-      <c r="C54">
+      <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="s">
         <v>29</v>
       </c>
-      <c r="E54">
+      <c r="E54" t="n">
         <v>107236</v>
       </c>
-      <c r="F54">
+      <c r="F54" t="n">
         <v>1.8181652889999999E-5</v>
       </c>
-      <c r="G54">
+      <c r="G54" t="n">
         <v>1.818165289E-4</v>
       </c>
       <c r="H54" t="s">
@@ -2402,26 +2578,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="A55" t="s">
         <v>40</v>
       </c>
-      <c r="B55">
+      <c r="B55" t="n">
         <v>2015</v>
       </c>
-      <c r="C55">
+      <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" t="s">
         <v>29</v>
       </c>
-      <c r="E55">
+      <c r="E55" t="n">
         <v>107254</v>
       </c>
-      <c r="F55">
+      <c r="F55" t="n">
         <v>6.181761984E-4</v>
       </c>
-      <c r="G55">
+      <c r="G55" t="n">
         <v>6.7672112069999998E-2</v>
       </c>
       <c r="H55" t="s">
@@ -2431,26 +2607,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="A56" t="s">
         <v>40</v>
       </c>
-      <c r="B56">
+      <c r="B56" t="n">
         <v>2015</v>
       </c>
-      <c r="C56">
+      <c r="C56" t="n">
         <v>1</v>
       </c>
       <c r="D56" t="s">
         <v>29</v>
       </c>
-      <c r="E56">
+      <c r="E56" t="n">
         <v>107292</v>
       </c>
-      <c r="F56">
+      <c r="F56" t="n">
         <v>1.090899174E-4</v>
       </c>
-      <c r="G56">
+      <c r="G56" t="n">
         <v>9.0908264469999995E-5</v>
       </c>
       <c r="H56" t="s">
@@ -2460,26 +2636,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="A57" t="s">
         <v>40</v>
       </c>
-      <c r="B57">
+      <c r="B57" t="n">
         <v>2015</v>
       </c>
-      <c r="C57">
+      <c r="C57" t="n">
         <v>1</v>
       </c>
       <c r="D57" t="s">
         <v>29</v>
       </c>
-      <c r="E57">
+      <c r="E57" t="n">
         <v>107342</v>
       </c>
-      <c r="F57">
+      <c r="F57" t="n">
         <v>3.6363305790000001E-5</v>
       </c>
-      <c r="G57">
+      <c r="G57" t="n">
         <v>1.8181652889999999E-5</v>
       </c>
       <c r="H57" t="s">
@@ -2489,26 +2665,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="A58" t="s">
         <v>40</v>
       </c>
-      <c r="B58">
+      <c r="B58" t="n">
         <v>2015</v>
       </c>
-      <c r="C58">
+      <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="s">
         <v>29</v>
       </c>
-      <c r="E58">
+      <c r="E58" t="n">
         <v>107564</v>
       </c>
-      <c r="F58">
+      <c r="F58" t="n">
         <v>1.8181652889999999E-5</v>
       </c>
-      <c r="G58">
+      <c r="G58" t="n">
         <v>1.8181652889999999E-5</v>
       </c>
       <c r="H58" t="s">
@@ -2518,26 +2694,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59" t="s">
         <v>40</v>
       </c>
-      <c r="B59">
+      <c r="B59" t="n">
         <v>2015</v>
       </c>
-      <c r="C59">
+      <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="s">
         <v>29</v>
       </c>
-      <c r="E59">
+      <c r="E59" t="n">
         <v>107643</v>
       </c>
-      <c r="F59">
+      <c r="F59" t="n">
         <v>4.3635966950000002E-4</v>
       </c>
-      <c r="G59">
+      <c r="G59" t="n">
         <v>1.527258843E-3</v>
       </c>
       <c r="H59" t="s">
@@ -2547,26 +2723,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="A60" t="s">
         <v>40</v>
       </c>
-      <c r="B60">
+      <c r="B60" t="n">
         <v>2015</v>
       </c>
-      <c r="C60">
+      <c r="C60" t="n">
         <v>1</v>
       </c>
       <c r="D60" t="s">
         <v>29</v>
       </c>
-      <c r="E60">
+      <c r="E60" t="n">
         <v>107661</v>
       </c>
-      <c r="F60">
+      <c r="F60" t="n">
         <v>3.6363305790000001E-5</v>
       </c>
-      <c r="G60">
+      <c r="G60" t="n">
         <v>2.181798347E-4</v>
       </c>
       <c r="H60" t="s">
@@ -2576,26 +2752,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61">
       <c r="A61" t="s">
         <v>40</v>
       </c>
-      <c r="B61">
+      <c r="B61" t="n">
         <v>2015</v>
       </c>
-      <c r="C61">
+      <c r="C61" t="n">
         <v>1</v>
       </c>
       <c r="D61" t="s">
         <v>29</v>
       </c>
-      <c r="E61">
+      <c r="E61" t="n">
         <v>107677</v>
       </c>
-      <c r="F61">
+      <c r="F61" t="n">
         <v>9.272642976E-4</v>
       </c>
-      <c r="G61">
+      <c r="G61" t="n">
         <v>1.072717521E-3</v>
       </c>
       <c r="H61" t="s">
@@ -2605,26 +2781,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62">
       <c r="A62" t="s">
         <v>40</v>
       </c>
-      <c r="B62">
+      <c r="B62" t="n">
         <v>2015</v>
       </c>
-      <c r="C62">
+      <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="s">
         <v>29</v>
       </c>
-      <c r="E62">
+      <c r="E62" t="n">
         <v>107696</v>
       </c>
-      <c r="F62">
+      <c r="F62" t="n">
         <v>5.454495868E-5</v>
       </c>
-      <c r="G62">
+      <c r="G62" t="n">
         <v>7.2726611580000003E-5</v>
       </c>
       <c r="H62" t="s">
@@ -2634,26 +2810,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63">
       <c r="A63" t="s">
         <v>40</v>
       </c>
-      <c r="B63">
+      <c r="B63" t="n">
         <v>2015</v>
       </c>
-      <c r="C63">
+      <c r="C63" t="n">
         <v>1</v>
       </c>
       <c r="D63" t="s">
         <v>29</v>
       </c>
-      <c r="E63">
+      <c r="E63" t="n">
         <v>123867</v>
       </c>
-      <c r="F63">
+      <c r="F63" t="n">
         <v>3.9999636369999998E-4</v>
       </c>
-      <c r="G63">
+      <c r="G63" t="n">
         <v>8.1817438020000003E-4</v>
       </c>
       <c r="H63" t="s">
@@ -2663,26 +2839,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64">
       <c r="A64" t="s">
         <v>40</v>
       </c>
-      <c r="B64">
+      <c r="B64" t="n">
         <v>2015</v>
       </c>
-      <c r="C64">
+      <c r="C64" t="n">
         <v>1</v>
       </c>
       <c r="D64" t="s">
         <v>29</v>
       </c>
-      <c r="E64">
+      <c r="E64" t="n">
         <v>124224</v>
       </c>
-      <c r="F64">
+      <c r="F64" t="n">
         <v>3.6363305790000001E-5</v>
       </c>
-      <c r="G64">
+      <c r="G64" t="n">
         <v>1.8181652889999999E-5</v>
       </c>
       <c r="H64" t="s">
@@ -2692,26 +2868,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65">
       <c r="A65" t="s">
         <v>40</v>
       </c>
-      <c r="B65">
+      <c r="B65" t="n">
         <v>2015</v>
       </c>
-      <c r="C65">
+      <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="s">
         <v>29</v>
       </c>
-      <c r="E65">
+      <c r="E65" t="n">
         <v>124535</v>
       </c>
-      <c r="F65">
+      <c r="F65" t="n">
         <v>1.8181652889999999E-5</v>
       </c>
-      <c r="G65">
+      <c r="G65" t="n">
         <v>3.436332397E-3</v>
       </c>
       <c r="H65" t="s">
@@ -2721,26 +2897,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66">
       <c r="A66" t="s">
         <v>40</v>
       </c>
-      <c r="B66">
+      <c r="B66" t="n">
         <v>2015</v>
       </c>
-      <c r="C66">
+      <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="s">
         <v>29</v>
       </c>
-      <c r="E66">
+      <c r="E66" t="n">
         <v>124929</v>
       </c>
-      <c r="F66">
+      <c r="F66" t="n">
         <v>2.5454314050000001E-4</v>
       </c>
-      <c r="G66">
+      <c r="G66" t="n">
         <v>1.2545340500000001E-3</v>
       </c>
       <c r="H66" t="s">
@@ -2750,26 +2926,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67">
       <c r="A67" t="s">
         <v>40</v>
       </c>
-      <c r="B67">
+      <c r="B67" t="n">
         <v>2015</v>
       </c>
-      <c r="C67">
+      <c r="C67" t="n">
         <v>1</v>
       </c>
       <c r="D67" t="s">
         <v>29</v>
       </c>
-      <c r="E67">
+      <c r="E67" t="n">
         <v>124951</v>
       </c>
-      <c r="F67">
+      <c r="F67" t="n">
         <v>3.6363305790000001E-5</v>
       </c>
-      <c r="G67">
+      <c r="G67" t="n">
         <v>2.3636148759999999E-4</v>
       </c>
       <c r="H67" t="s">
@@ -2779,26 +2955,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68">
       <c r="A68" t="s">
         <v>40</v>
       </c>
-      <c r="B68">
+      <c r="B68" t="n">
         <v>2015</v>
       </c>
-      <c r="C68">
+      <c r="C68" t="n">
         <v>1</v>
       </c>
       <c r="D68" t="s">
         <v>29</v>
       </c>
-      <c r="E68">
+      <c r="E68" t="n">
         <v>128506</v>
       </c>
-      <c r="F68">
+      <c r="F68" t="n">
         <v>9.0908264469999995E-5</v>
       </c>
-      <c r="G68">
+      <c r="G68" t="n">
         <v>5.9999454549999995E-4</v>
       </c>
       <c r="H68" t="s">
@@ -2808,26 +2984,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69">
       <c r="A69" t="s">
         <v>40</v>
       </c>
-      <c r="B69">
+      <c r="B69" t="n">
         <v>2015</v>
       </c>
-      <c r="C69">
+      <c r="C69" t="n">
         <v>1</v>
       </c>
       <c r="D69" t="s">
         <v>29</v>
       </c>
-      <c r="E69">
+      <c r="E69" t="n">
         <v>138899</v>
       </c>
-      <c r="F69">
+      <c r="F69" t="n">
         <v>3.6363305790000001E-5</v>
       </c>
-      <c r="G69">
+      <c r="G69" t="n">
         <v>3.4545140499999999E-4</v>
       </c>
       <c r="H69" t="s">
@@ -2837,26 +3013,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70">
       <c r="A70" t="s">
         <v>40</v>
       </c>
-      <c r="B70">
+      <c r="B70" t="n">
         <v>2015</v>
       </c>
-      <c r="C70">
+      <c r="C70" t="n">
         <v>1</v>
       </c>
       <c r="D70" t="s">
         <v>29</v>
       </c>
-      <c r="E70">
+      <c r="E70" t="n">
         <v>139024</v>
       </c>
-      <c r="F70">
+      <c r="F70" t="n">
         <v>1.8181652889999999E-5</v>
       </c>
-      <c r="G70">
+      <c r="G70" t="n">
         <v>1.072717521E-3</v>
       </c>
       <c r="H70" t="s">
@@ -2866,26 +3042,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71">
       <c r="A71" t="s">
         <v>40</v>
       </c>
-      <c r="B71">
+      <c r="B71" t="n">
         <v>2015</v>
       </c>
-      <c r="C71">
+      <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="s">
         <v>29</v>
       </c>
-      <c r="E71">
+      <c r="E71" t="n">
         <v>149898</v>
       </c>
-      <c r="F71">
+      <c r="F71" t="n">
         <v>5.454495868E-5</v>
       </c>
-      <c r="G71">
+      <c r="G71" t="n">
         <v>4.1999618190000001E-3</v>
       </c>
       <c r="H71" t="s">
@@ -2895,26 +3071,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72">
       <c r="A72" t="s">
         <v>40</v>
       </c>
-      <c r="B72">
+      <c r="B72" t="n">
         <v>2015</v>
       </c>
-      <c r="C72">
+      <c r="C72" t="n">
         <v>1</v>
       </c>
       <c r="D72" t="s">
         <v>29</v>
       </c>
-      <c r="E72">
+      <c r="E72" t="n">
         <v>178639</v>
       </c>
-      <c r="F72">
+      <c r="F72" t="n">
         <v>1.8181652889999999E-5</v>
       </c>
-      <c r="G72">
+      <c r="G72" t="n">
         <v>5.454495868E-5</v>
       </c>
       <c r="H72" t="s">
@@ -2924,26 +3100,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="A73" t="s">
         <v>40</v>
       </c>
-      <c r="B73">
+      <c r="B73" t="n">
         <v>2015</v>
       </c>
-      <c r="C73">
+      <c r="C73" t="n">
         <v>1</v>
       </c>
       <c r="D73" t="s">
         <v>29</v>
       </c>
-      <c r="E73">
+      <c r="E73" t="n">
         <v>532031</v>
       </c>
-      <c r="F73">
+      <c r="F73" t="n">
         <v>1.8181652889999999E-5</v>
       </c>
-      <c r="G73">
+      <c r="G73" t="n">
         <v>1.4545322319999999E-4</v>
       </c>
       <c r="H73" t="s">
@@ -2953,26 +3129,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74">
       <c r="A74" t="s">
         <v>40</v>
       </c>
-      <c r="B74">
+      <c r="B74" t="n">
         <v>2016</v>
       </c>
-      <c r="C74">
+      <c r="C74" t="n">
         <v>1</v>
       </c>
       <c r="D74" t="s">
         <v>29</v>
       </c>
-      <c r="E74">
+      <c r="E74" t="n">
         <v>100930</v>
       </c>
-      <c r="F74">
+      <c r="F74" t="n">
         <v>3.66405859E-5</v>
       </c>
-      <c r="G74">
+      <c r="G74" t="n">
         <v>1.4656234360000001E-3</v>
       </c>
       <c r="H74" t="s">
@@ -2982,26 +3158,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75">
       <c r="A75" t="s">
         <v>40</v>
       </c>
-      <c r="B75">
+      <c r="B75" t="n">
         <v>2016</v>
       </c>
-      <c r="C75">
+      <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="s">
         <v>29</v>
       </c>
-      <c r="E75">
+      <c r="E75" t="n">
         <v>100931</v>
       </c>
-      <c r="F75">
+      <c r="F75" t="n">
         <v>5.4960878849999999E-5</v>
       </c>
-      <c r="G75">
+      <c r="G75" t="n">
         <v>9.1601464740000003E-5</v>
       </c>
       <c r="H75" t="s">
@@ -3011,26 +3187,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76">
       <c r="A76" t="s">
         <v>40</v>
       </c>
-      <c r="B76">
+      <c r="B76" t="n">
         <v>2016</v>
       </c>
-      <c r="C76">
+      <c r="C76" t="n">
         <v>1</v>
       </c>
       <c r="D76" t="s">
         <v>29</v>
       </c>
-      <c r="E76">
+      <c r="E76" t="n">
         <v>107230</v>
       </c>
-      <c r="F76">
+      <c r="F76" t="n">
         <v>3.66405859E-5</v>
       </c>
-      <c r="G76">
+      <c r="G76" t="n">
         <v>1.282420506E-4</v>
       </c>
       <c r="H76" t="s">
@@ -3040,26 +3216,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77">
       <c r="A77" t="s">
         <v>40</v>
       </c>
-      <c r="B77">
+      <c r="B77" t="n">
         <v>2016</v>
       </c>
-      <c r="C77">
+      <c r="C77" t="n">
         <v>1</v>
       </c>
       <c r="D77" t="s">
         <v>29</v>
       </c>
-      <c r="E77">
+      <c r="E77" t="n">
         <v>107254</v>
       </c>
-      <c r="F77">
+      <c r="F77" t="n">
         <v>5.4960878849999999E-5</v>
       </c>
-      <c r="G77">
+      <c r="G77" t="n">
         <v>8.2441318269999998E-3</v>
       </c>
       <c r="H77" t="s">
@@ -3069,26 +3245,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78">
       <c r="A78" t="s">
         <v>40</v>
       </c>
-      <c r="B78">
+      <c r="B78" t="n">
         <v>2016</v>
       </c>
-      <c r="C78">
+      <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="s">
         <v>29</v>
       </c>
-      <c r="E78">
+      <c r="E78" t="n">
         <v>107292</v>
       </c>
-      <c r="F78">
+      <c r="F78" t="n">
         <v>9.1601464740000003E-5</v>
       </c>
-      <c r="G78">
+      <c r="G78" t="n">
         <v>5.4960878849999999E-5</v>
       </c>
       <c r="H78" t="s">
@@ -3098,26 +3274,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79">
       <c r="A79" t="s">
         <v>40</v>
       </c>
-      <c r="B79">
+      <c r="B79" t="n">
         <v>2016</v>
       </c>
-      <c r="C79">
+      <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="s">
         <v>29</v>
       </c>
-      <c r="E79">
+      <c r="E79" t="n">
         <v>107342</v>
       </c>
-      <c r="F79">
+      <c r="F79" t="n">
         <v>3.66405859E-5</v>
       </c>
-      <c r="G79">
+      <c r="G79" t="n">
         <v>1.832029295E-5</v>
       </c>
       <c r="H79" t="s">
@@ -3127,26 +3303,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80">
       <c r="A80" t="s">
         <v>40</v>
       </c>
-      <c r="B80">
+      <c r="B80" t="n">
         <v>2016</v>
       </c>
-      <c r="C80">
+      <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="s">
         <v>29</v>
       </c>
-      <c r="E80">
+      <c r="E80" t="n">
         <v>107643</v>
       </c>
-      <c r="F80">
+      <c r="F80" t="n">
         <v>1.465623436E-4</v>
       </c>
-      <c r="G80">
+      <c r="G80" t="n">
         <v>7.694523039E-4</v>
       </c>
       <c r="H80" t="s">
@@ -3156,26 +3332,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81">
       <c r="A81" t="s">
         <v>40</v>
       </c>
-      <c r="B81">
+      <c r="B81" t="n">
         <v>2016</v>
       </c>
-      <c r="C81">
+      <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="s">
         <v>29</v>
       </c>
-      <c r="E81">
+      <c r="E81" t="n">
         <v>107677</v>
       </c>
-      <c r="F81">
+      <c r="F81" t="n">
         <v>2.198435154E-4</v>
       </c>
-      <c r="G81">
+      <c r="G81" t="n">
         <v>2.198435154E-4</v>
       </c>
       <c r="H81" t="s">
@@ -3185,26 +3361,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82">
       <c r="A82" t="s">
         <v>40</v>
       </c>
-      <c r="B82">
+      <c r="B82" t="n">
         <v>2016</v>
       </c>
-      <c r="C82">
+      <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="s">
         <v>29</v>
       </c>
-      <c r="E82">
+      <c r="E82" t="n">
         <v>107696</v>
       </c>
-      <c r="F82">
+      <c r="F82" t="n">
         <v>5.4960878849999999E-5</v>
       </c>
-      <c r="G82">
+      <c r="G82" t="n">
         <v>1.8320292950000001E-4</v>
       </c>
       <c r="H82" t="s">
@@ -3214,26 +3390,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83">
       <c r="A83" t="s">
         <v>40</v>
       </c>
-      <c r="B83">
+      <c r="B83" t="n">
         <v>2016</v>
       </c>
-      <c r="C83">
+      <c r="C83" t="n">
         <v>1</v>
       </c>
       <c r="D83" t="s">
         <v>29</v>
       </c>
-      <c r="E83">
+      <c r="E83" t="n">
         <v>123867</v>
       </c>
-      <c r="F83">
+      <c r="F83" t="n">
         <v>5.4960878849999999E-5</v>
       </c>
-      <c r="G83">
+      <c r="G83" t="n">
         <v>9.1601464740000003E-5</v>
       </c>
       <c r="H83" t="s">
@@ -3243,26 +3419,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84">
       <c r="A84" t="s">
         <v>40</v>
       </c>
-      <c r="B84">
+      <c r="B84" t="n">
         <v>2016</v>
       </c>
-      <c r="C84">
+      <c r="C84" t="n">
         <v>1</v>
       </c>
       <c r="D84" t="s">
         <v>29</v>
       </c>
-      <c r="E84">
+      <c r="E84" t="n">
         <v>124257</v>
       </c>
-      <c r="F84">
+      <c r="F84" t="n">
         <v>1.832029295E-5</v>
       </c>
-      <c r="G84">
+      <c r="G84" t="n">
         <v>9.3433494040000005E-4</v>
       </c>
       <c r="H84" t="s">
@@ -3272,26 +3448,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85">
       <c r="A85" t="s">
         <v>40</v>
       </c>
-      <c r="B85">
+      <c r="B85" t="n">
         <v>2016</v>
       </c>
-      <c r="C85">
+      <c r="C85" t="n">
         <v>1</v>
       </c>
       <c r="D85" t="s">
         <v>29</v>
       </c>
-      <c r="E85">
+      <c r="E85" t="n">
         <v>124929</v>
       </c>
-      <c r="F85">
+      <c r="F85" t="n">
         <v>3.66405859E-5</v>
       </c>
-      <c r="G85">
+      <c r="G85" t="n">
         <v>2.7480439419999997E-4</v>
       </c>
       <c r="H85" t="s">
@@ -3301,26 +3477,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86">
       <c r="A86" t="s">
         <v>40</v>
       </c>
-      <c r="B86">
+      <c r="B86" t="n">
         <v>2016</v>
       </c>
-      <c r="C86">
+      <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="s">
         <v>29</v>
       </c>
-      <c r="E86">
+      <c r="E86" t="n">
         <v>124951</v>
       </c>
-      <c r="F86">
+      <c r="F86" t="n">
         <v>2.3816380829999999E-4</v>
       </c>
-      <c r="G86">
+      <c r="G86" t="n">
         <v>1.410662557E-3</v>
       </c>
       <c r="H86" t="s">
@@ -3330,26 +3506,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87">
       <c r="A87" t="s">
         <v>40</v>
       </c>
-      <c r="B87">
+      <c r="B87" t="n">
         <v>2016</v>
       </c>
-      <c r="C87">
+      <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="s">
         <v>29</v>
       </c>
-      <c r="E87">
+      <c r="E87" t="n">
         <v>128506</v>
       </c>
-      <c r="F87">
+      <c r="F87" t="n">
         <v>1.282420506E-4</v>
       </c>
-      <c r="G87">
+      <c r="G87" t="n">
         <v>1.1908190419999999E-3</v>
       </c>
       <c r="H87" t="s">
@@ -3359,26 +3535,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88">
       <c r="A88" t="s">
         <v>40</v>
       </c>
-      <c r="B88">
+      <c r="B88" t="n">
         <v>2016</v>
       </c>
-      <c r="C88">
+      <c r="C88" t="n">
         <v>1</v>
       </c>
       <c r="D88" t="s">
         <v>29</v>
       </c>
-      <c r="E88">
+      <c r="E88" t="n">
         <v>132511</v>
       </c>
-      <c r="F88">
+      <c r="F88" t="n">
         <v>3.66405859E-5</v>
       </c>
-      <c r="G88">
+      <c r="G88" t="n">
         <v>5.8624937439999999E-4</v>
       </c>
       <c r="H88" t="s">
@@ -3388,26 +3564,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89">
       <c r="A89" t="s">
         <v>40</v>
       </c>
-      <c r="B89">
+      <c r="B89" t="n">
         <v>2016</v>
       </c>
-      <c r="C89">
+      <c r="C89" t="n">
         <v>1</v>
       </c>
       <c r="D89" t="s">
         <v>29</v>
       </c>
-      <c r="E89">
+      <c r="E89" t="n">
         <v>381759</v>
       </c>
-      <c r="F89">
+      <c r="F89" t="n">
         <v>1.832029295E-5</v>
       </c>
-      <c r="G89">
+      <c r="G89" t="n">
         <v>1.92363076E-3</v>
       </c>
       <c r="H89" t="s">
@@ -3417,26 +3593,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90">
       <c r="A90" t="s">
         <v>40</v>
       </c>
-      <c r="B90">
+      <c r="B90" t="n">
         <v>2016</v>
       </c>
-      <c r="C90">
+      <c r="C90" t="n">
         <v>1</v>
       </c>
       <c r="D90" t="s">
         <v>29</v>
       </c>
-      <c r="E90">
+      <c r="E90" t="n">
         <v>532031</v>
       </c>
-      <c r="F90">
+      <c r="F90" t="n">
         <v>1.832029295E-5</v>
       </c>
-      <c r="G90">
+      <c r="G90" t="n">
         <v>1.8320292950000001E-4</v>
       </c>
       <c r="H90" t="s">
@@ -3446,26 +3622,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91">
       <c r="A91" t="s">
         <v>40</v>
       </c>
-      <c r="B91">
+      <c r="B91" t="n">
         <v>2017</v>
       </c>
-      <c r="C91">
+      <c r="C91" t="n">
         <v>1</v>
       </c>
       <c r="D91" t="s">
         <v>29</v>
       </c>
-      <c r="E91">
+      <c r="E91" t="n">
         <v>100930</v>
       </c>
-      <c r="F91">
+      <c r="F91" t="n">
         <v>1.8181652889999999E-5</v>
       </c>
-      <c r="G91">
+      <c r="G91" t="n">
         <v>8.3635603309999997E-4</v>
       </c>
       <c r="H91" t="s">
@@ -3475,26 +3651,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92">
       <c r="A92" t="s">
         <v>40</v>
       </c>
-      <c r="B92">
+      <c r="B92" t="n">
         <v>2017</v>
       </c>
-      <c r="C92">
+      <c r="C92" t="n">
         <v>1</v>
       </c>
       <c r="D92" t="s">
         <v>29</v>
       </c>
-      <c r="E92">
+      <c r="E92" t="n">
         <v>106834</v>
       </c>
-      <c r="F92">
+      <c r="F92" t="n">
         <v>1.8181652889999999E-5</v>
       </c>
-      <c r="G92">
+      <c r="G92" t="n">
         <v>1.8181652889999999E-5</v>
       </c>
       <c r="H92" t="s">
@@ -3504,26 +3680,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93">
       <c r="A93" t="s">
         <v>40</v>
       </c>
-      <c r="B93">
+      <c r="B93" t="n">
         <v>2017</v>
       </c>
-      <c r="C93">
+      <c r="C93" t="n">
         <v>1</v>
       </c>
       <c r="D93" t="s">
         <v>29</v>
       </c>
-      <c r="E93">
+      <c r="E93" t="n">
         <v>107254</v>
       </c>
-      <c r="F93">
+      <c r="F93" t="n">
         <v>2.5454314050000001E-4</v>
       </c>
-      <c r="G93">
+      <c r="G93" t="n">
         <v>9.0908264469999993E-3</v>
       </c>
       <c r="H93" t="s">
@@ -3533,26 +3709,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94">
       <c r="A94" t="s">
         <v>40</v>
       </c>
-      <c r="B94">
+      <c r="B94" t="n">
         <v>2017</v>
       </c>
-      <c r="C94">
+      <c r="C94" t="n">
         <v>1</v>
       </c>
       <c r="D94" t="s">
         <v>29</v>
       </c>
-      <c r="E94">
+      <c r="E94" t="n">
         <v>107292</v>
       </c>
-      <c r="F94">
+      <c r="F94" t="n">
         <v>1.8181652889999999E-5</v>
       </c>
-      <c r="G94">
+      <c r="G94" t="n">
         <v>3.6363305790000001E-5</v>
       </c>
       <c r="H94" t="s">
@@ -3562,26 +3738,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95">
       <c r="A95" t="s">
         <v>40</v>
       </c>
-      <c r="B95">
+      <c r="B95" t="n">
         <v>2017</v>
       </c>
-      <c r="C95">
+      <c r="C95" t="n">
         <v>1</v>
       </c>
       <c r="D95" t="s">
         <v>29</v>
       </c>
-      <c r="E95">
+      <c r="E95" t="n">
         <v>107643</v>
       </c>
-      <c r="F95">
+      <c r="F95" t="n">
         <v>1.999981818E-4</v>
       </c>
-      <c r="G95">
+      <c r="G95" t="n">
         <v>1.1636257850000001E-3</v>
       </c>
       <c r="H95" t="s">
@@ -3591,26 +3767,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96">
       <c r="A96" t="s">
         <v>40</v>
       </c>
-      <c r="B96">
+      <c r="B96" t="n">
         <v>2017</v>
       </c>
-      <c r="C96">
+      <c r="C96" t="n">
         <v>1</v>
       </c>
       <c r="D96" t="s">
         <v>29</v>
       </c>
-      <c r="E96">
+      <c r="E96" t="n">
         <v>107677</v>
       </c>
-      <c r="F96">
+      <c r="F96" t="n">
         <v>4.5454132240000002E-4</v>
       </c>
-      <c r="G96">
+      <c r="G96" t="n">
         <v>4.3635966950000002E-4</v>
       </c>
       <c r="H96" t="s">
@@ -3620,26 +3796,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97">
       <c r="A97" t="s">
         <v>40</v>
       </c>
-      <c r="B97">
+      <c r="B97" t="n">
         <v>2017</v>
       </c>
-      <c r="C97">
+      <c r="C97" t="n">
         <v>1</v>
       </c>
       <c r="D97" t="s">
         <v>29</v>
       </c>
-      <c r="E97">
+      <c r="E97" t="n">
         <v>123867</v>
       </c>
-      <c r="F97">
+      <c r="F97" t="n">
         <v>3.6363305790000001E-5</v>
       </c>
-      <c r="G97">
+      <c r="G97" t="n">
         <v>9.0908264469999995E-5</v>
       </c>
       <c r="H97" t="s">
@@ -3649,26 +3825,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98">
       <c r="A98" t="s">
         <v>40</v>
       </c>
-      <c r="B98">
+      <c r="B98" t="n">
         <v>2017</v>
       </c>
-      <c r="C98">
+      <c r="C98" t="n">
         <v>1</v>
       </c>
       <c r="D98" t="s">
         <v>29</v>
       </c>
-      <c r="E98">
+      <c r="E98" t="n">
         <v>124224</v>
       </c>
-      <c r="F98">
+      <c r="F98" t="n">
         <v>1.818165289E-4</v>
       </c>
-      <c r="G98">
+      <c r="G98" t="n">
         <v>1.4545322319999999E-4</v>
       </c>
       <c r="H98" t="s">
@@ -3678,26 +3854,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99">
       <c r="A99" t="s">
         <v>40</v>
       </c>
-      <c r="B99">
+      <c r="B99" t="n">
         <v>2017</v>
       </c>
-      <c r="C99">
+      <c r="C99" t="n">
         <v>1</v>
       </c>
       <c r="D99" t="s">
         <v>29</v>
       </c>
-      <c r="E99">
+      <c r="E99" t="n">
         <v>124257</v>
       </c>
-      <c r="F99">
+      <c r="F99" t="n">
         <v>1.8181652889999999E-5</v>
       </c>
-      <c r="G99">
+      <c r="G99" t="n">
         <v>1.3454423139999999E-3</v>
       </c>
       <c r="H99" t="s">
@@ -3707,26 +3883,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100">
       <c r="A100" t="s">
         <v>40</v>
       </c>
-      <c r="B100">
+      <c r="B100" t="n">
         <v>2017</v>
       </c>
-      <c r="C100">
+      <c r="C100" t="n">
         <v>1</v>
       </c>
       <c r="D100" t="s">
         <v>29</v>
       </c>
-      <c r="E100">
+      <c r="E100" t="n">
         <v>124929</v>
       </c>
-      <c r="F100">
+      <c r="F100" t="n">
         <v>3.6363305790000001E-5</v>
       </c>
-      <c r="G100">
+      <c r="G100" t="n">
         <v>2.3636148759999999E-4</v>
       </c>
       <c r="H100" t="s">
@@ -3736,26 +3912,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101">
       <c r="A101" t="s">
         <v>40</v>
       </c>
-      <c r="B101">
+      <c r="B101" t="n">
         <v>2017</v>
       </c>
-      <c r="C101">
+      <c r="C101" t="n">
         <v>1</v>
       </c>
       <c r="D101" t="s">
         <v>29</v>
       </c>
-      <c r="E101">
+      <c r="E101" t="n">
         <v>125131</v>
       </c>
-      <c r="F101">
+      <c r="F101" t="n">
         <v>1.8181652889999999E-5</v>
       </c>
-      <c r="G101">
+      <c r="G101" t="n">
         <v>5.454495868E-5</v>
       </c>
       <c r="H101" t="s">
@@ -3765,26 +3941,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102">
       <c r="A102" t="s">
         <v>40</v>
       </c>
-      <c r="B102">
+      <c r="B102" t="n">
         <v>2017</v>
       </c>
-      <c r="C102">
+      <c r="C102" t="n">
         <v>1</v>
       </c>
       <c r="D102" t="s">
         <v>29</v>
       </c>
-      <c r="E102">
+      <c r="E102" t="n">
         <v>128506</v>
       </c>
-      <c r="F102">
+      <c r="F102" t="n">
         <v>3.6363305790000001E-5</v>
       </c>
-      <c r="G102">
+      <c r="G102" t="n">
         <v>1.090899174E-4</v>
       </c>
       <c r="H102" t="s">
@@ -3794,26 +3970,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103">
       <c r="A103" t="s">
         <v>40</v>
       </c>
-      <c r="B103">
+      <c r="B103" t="n">
         <v>2017</v>
       </c>
-      <c r="C103">
+      <c r="C103" t="n">
         <v>1</v>
       </c>
       <c r="D103" t="s">
         <v>29</v>
       </c>
-      <c r="E103">
+      <c r="E103" t="n">
         <v>139488</v>
       </c>
-      <c r="F103">
+      <c r="F103" t="n">
         <v>1.8181652889999999E-5</v>
       </c>
-      <c r="G103">
+      <c r="G103" t="n">
         <v>5.454495868E-5</v>
       </c>
       <c r="H103" t="s">
@@ -3823,26 +3999,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104">
       <c r="A104" t="s">
         <v>40</v>
       </c>
-      <c r="B104">
+      <c r="B104" t="n">
         <v>2017</v>
       </c>
-      <c r="C104">
+      <c r="C104" t="n">
         <v>1</v>
       </c>
       <c r="D104" t="s">
         <v>29</v>
       </c>
-      <c r="E104">
+      <c r="E104" t="n">
         <v>149898</v>
       </c>
-      <c r="F104">
+      <c r="F104" t="n">
         <v>5.454495868E-5</v>
       </c>
-      <c r="G104">
+      <c r="G104" t="n">
         <v>6.1272170250000002E-3</v>
       </c>
       <c r="H104" t="s">
@@ -3852,26 +4028,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105">
       <c r="A105" t="s">
         <v>40</v>
       </c>
-      <c r="B105">
+      <c r="B105" t="n">
         <v>2017</v>
       </c>
-      <c r="C105">
+      <c r="C105" t="n">
         <v>1</v>
       </c>
       <c r="D105" t="s">
         <v>29</v>
       </c>
-      <c r="E105">
+      <c r="E105" t="n">
         <v>178639</v>
       </c>
-      <c r="F105">
+      <c r="F105" t="n">
         <v>1.8181652889999999E-5</v>
       </c>
-      <c r="G105">
+      <c r="G105" t="n">
         <v>5.454495868E-5</v>
       </c>
       <c r="H105" t="s">
@@ -3881,26 +4057,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106">
       <c r="A106" t="s">
         <v>40</v>
       </c>
-      <c r="B106">
+      <c r="B106" t="n">
         <v>2017</v>
       </c>
-      <c r="C106">
+      <c r="C106" t="n">
         <v>1</v>
       </c>
       <c r="D106" t="s">
         <v>29</v>
       </c>
-      <c r="E106">
+      <c r="E106" t="n">
         <v>532031</v>
       </c>
-      <c r="F106">
+      <c r="F106" t="n">
         <v>3.8181471079999998E-4</v>
       </c>
-      <c r="G106">
+      <c r="G106" t="n">
         <v>6.9090280999999998E-3</v>
       </c>
       <c r="H106" t="s">
@@ -3910,26 +4086,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107">
       <c r="A107" t="s">
         <v>40</v>
       </c>
-      <c r="B107">
+      <c r="B107" t="n">
         <v>2018</v>
       </c>
-      <c r="C107">
+      <c r="C107" t="n">
         <v>1</v>
       </c>
       <c r="D107" t="s">
         <v>29</v>
       </c>
-      <c r="E107">
+      <c r="E107" t="n">
         <v>100930</v>
       </c>
-      <c r="F107">
+      <c r="F107" t="n">
         <v>7.3068916409999994E-5</v>
       </c>
-      <c r="G107">
+      <c r="G107" t="n">
         <v>2.7400843650000001E-3</v>
       </c>
       <c r="H107" t="s">
@@ -3939,26 +4115,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108">
       <c r="A108" t="s">
         <v>40</v>
       </c>
-      <c r="B108">
+      <c r="B108" t="n">
         <v>2018</v>
       </c>
-      <c r="C108">
+      <c r="C108" t="n">
         <v>1</v>
       </c>
       <c r="D108" t="s">
         <v>29</v>
       </c>
-      <c r="E108">
+      <c r="E108" t="n">
         <v>107120</v>
       </c>
-      <c r="F108">
+      <c r="F108" t="n">
         <v>1.8267229100000001E-5</v>
       </c>
-      <c r="G108">
+      <c r="G108" t="n">
         <v>3.6534458200000002E-5</v>
       </c>
       <c r="H108" t="s">
@@ -3968,26 +4144,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109">
       <c r="A109" t="s">
         <v>40</v>
       </c>
-      <c r="B109">
+      <c r="B109" t="n">
         <v>2018</v>
       </c>
-      <c r="C109">
+      <c r="C109" t="n">
         <v>1</v>
       </c>
       <c r="D109" t="s">
         <v>29</v>
       </c>
-      <c r="E109">
+      <c r="E109" t="n">
         <v>107254</v>
       </c>
-      <c r="F109">
+      <c r="F109" t="n">
         <v>3.6534458200000002E-5</v>
       </c>
-      <c r="G109">
+      <c r="G109" t="n">
         <v>6.9780815169999998E-3</v>
       </c>
       <c r="H109" t="s">
@@ -3997,26 +4173,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110">
       <c r="A110" t="s">
         <v>40</v>
       </c>
-      <c r="B110">
+      <c r="B110" t="n">
         <v>2018</v>
       </c>
-      <c r="C110">
+      <c r="C110" t="n">
         <v>1</v>
       </c>
       <c r="D110" t="s">
         <v>29</v>
       </c>
-      <c r="E110">
+      <c r="E110" t="n">
         <v>107643</v>
       </c>
-      <c r="F110">
+      <c r="F110" t="n">
         <v>2.5574120739999998E-4</v>
       </c>
-      <c r="G110">
+      <c r="G110" t="n">
         <v>1.1143009749999999E-3</v>
       </c>
       <c r="H110" t="s">
@@ -4026,26 +4202,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111">
       <c r="A111" t="s">
         <v>40</v>
       </c>
-      <c r="B111">
+      <c r="B111" t="n">
         <v>2018</v>
       </c>
-      <c r="C111">
+      <c r="C111" t="n">
         <v>1</v>
       </c>
       <c r="D111" t="s">
         <v>29</v>
       </c>
-      <c r="E111">
+      <c r="E111" t="n">
         <v>107677</v>
       </c>
-      <c r="F111">
+      <c r="F111" t="n">
         <v>1.096033746E-4</v>
       </c>
-      <c r="G111">
+      <c r="G111" t="n">
         <v>1.8267229099999999E-4</v>
       </c>
       <c r="H111" t="s">
@@ -4055,26 +4231,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112">
       <c r="A112" t="s">
         <v>40</v>
       </c>
-      <c r="B112">
+      <c r="B112" t="n">
         <v>2018</v>
       </c>
-      <c r="C112">
+      <c r="C112" t="n">
         <v>1</v>
       </c>
       <c r="D112" t="s">
         <v>29</v>
       </c>
-      <c r="E112">
+      <c r="E112" t="n">
         <v>107696</v>
       </c>
-      <c r="F112">
+      <c r="F112" t="n">
         <v>1.8267229100000001E-5</v>
       </c>
-      <c r="G112">
+      <c r="G112" t="n">
         <v>5.4801687310000003E-5</v>
       </c>
       <c r="H112" t="s">
@@ -4084,26 +4260,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113">
       <c r="A113" t="s">
         <v>40</v>
       </c>
-      <c r="B113">
+      <c r="B113" t="n">
         <v>2018</v>
       </c>
-      <c r="C113">
+      <c r="C113" t="n">
         <v>1</v>
       </c>
       <c r="D113" t="s">
         <v>29</v>
       </c>
-      <c r="E113">
+      <c r="E113" t="n">
         <v>124257</v>
       </c>
-      <c r="F113">
+      <c r="F113" t="n">
         <v>1.8267229100000001E-5</v>
       </c>
-      <c r="G113">
+      <c r="G113" t="n">
         <v>9.8643037149999998E-4</v>
       </c>
       <c r="H113" t="s">
@@ -4113,26 +4289,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114">
       <c r="A114" t="s">
         <v>40</v>
       </c>
-      <c r="B114">
+      <c r="B114" t="n">
         <v>2018</v>
       </c>
-      <c r="C114">
+      <c r="C114" t="n">
         <v>1</v>
       </c>
       <c r="D114" t="s">
         <v>29</v>
       </c>
-      <c r="E114">
+      <c r="E114" t="n">
         <v>124535</v>
       </c>
-      <c r="F114">
+      <c r="F114" t="n">
         <v>5.4801687310000003E-5</v>
       </c>
-      <c r="G114">
+      <c r="G114" t="n">
         <v>9.2797523840000007E-3</v>
       </c>
       <c r="H114" t="s">
@@ -4142,26 +4318,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115">
       <c r="A115" t="s">
         <v>40</v>
       </c>
-      <c r="B115">
+      <c r="B115" t="n">
         <v>2018</v>
       </c>
-      <c r="C115">
+      <c r="C115" t="n">
         <v>1</v>
       </c>
       <c r="D115" t="s">
         <v>29</v>
       </c>
-      <c r="E115">
+      <c r="E115" t="n">
         <v>532031</v>
       </c>
-      <c r="F115">
+      <c r="F115" t="n">
         <v>9.4989591330000005E-4</v>
       </c>
-      <c r="G115">
+      <c r="G115" t="n">
         <v>3.7265147370000001E-2</v>
       </c>
       <c r="H115" t="s">
@@ -4171,26 +4347,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116">
       <c r="A116" t="s">
         <v>40</v>
       </c>
-      <c r="B116">
+      <c r="B116" t="n">
         <v>2019</v>
       </c>
-      <c r="C116">
+      <c r="C116" t="n">
         <v>1</v>
       </c>
       <c r="D116" t="s">
         <v>29</v>
       </c>
-      <c r="E116">
+      <c r="E116" t="n">
         <v>100930</v>
       </c>
-      <c r="F116">
+      <c r="F116" t="n">
         <v>9.4341972290000001E-5</v>
       </c>
-      <c r="G116">
+      <c r="G116" t="n">
         <v>3.5661265530000002E-3</v>
       </c>
       <c r="H116" t="s">
@@ -4200,26 +4376,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117">
       <c r="A117" t="s">
         <v>40</v>
       </c>
-      <c r="B117">
+      <c r="B117" t="n">
         <v>2019</v>
       </c>
-      <c r="C117">
+      <c r="C117" t="n">
         <v>1</v>
       </c>
       <c r="D117" t="s">
         <v>29</v>
       </c>
-      <c r="E117">
+      <c r="E117" t="n">
         <v>106204</v>
       </c>
-      <c r="F117">
+      <c r="F117" t="n">
         <v>1.8868394459999999E-5</v>
       </c>
-      <c r="G117">
+      <c r="G117" t="n">
         <v>3.7736788919999999E-5</v>
       </c>
       <c r="H117" t="s">
@@ -4229,26 +4405,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118">
       <c r="A118" t="s">
         <v>40</v>
       </c>
-      <c r="B118">
+      <c r="B118" t="n">
         <v>2019</v>
       </c>
-      <c r="C118">
+      <c r="C118" t="n">
         <v>1</v>
       </c>
       <c r="D118" t="s">
         <v>29</v>
       </c>
-      <c r="E118">
+      <c r="E118" t="n">
         <v>107230</v>
       </c>
-      <c r="F118">
+      <c r="F118" t="n">
         <v>1.8868394459999999E-5</v>
       </c>
-      <c r="G118">
+      <c r="G118" t="n">
         <v>5.6605183370000002E-5</v>
       </c>
       <c r="H118" t="s">
@@ -4258,26 +4434,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119">
       <c r="A119" t="s">
         <v>40</v>
       </c>
-      <c r="B119">
+      <c r="B119" t="n">
         <v>2019</v>
       </c>
-      <c r="C119">
+      <c r="C119" t="n">
         <v>1</v>
       </c>
       <c r="D119" t="s">
         <v>29</v>
       </c>
-      <c r="E119">
+      <c r="E119" t="n">
         <v>107254</v>
       </c>
-      <c r="F119">
+      <c r="F119" t="n">
         <v>1.8868394460000001E-4</v>
       </c>
-      <c r="G119">
+      <c r="G119" t="n">
         <v>1.1887088509999999E-2</v>
       </c>
       <c r="H119" t="s">
@@ -4287,26 +4463,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120">
       <c r="A120" t="s">
         <v>40</v>
       </c>
-      <c r="B120">
+      <c r="B120" t="n">
         <v>2019</v>
       </c>
-      <c r="C120">
+      <c r="C120" t="n">
         <v>1</v>
       </c>
       <c r="D120" t="s">
         <v>29</v>
       </c>
-      <c r="E120">
+      <c r="E120" t="n">
         <v>107292</v>
       </c>
-      <c r="F120">
+      <c r="F120" t="n">
         <v>1.8868394459999999E-5</v>
       </c>
-      <c r="G120">
+      <c r="G120" t="n">
         <v>1.8868394459999999E-5</v>
       </c>
       <c r="H120" t="s">
@@ -4316,26 +4492,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121">
       <c r="A121" t="s">
         <v>40</v>
       </c>
-      <c r="B121">
+      <c r="B121" t="n">
         <v>2019</v>
       </c>
-      <c r="C121">
+      <c r="C121" t="n">
         <v>1</v>
       </c>
       <c r="D121" t="s">
         <v>29</v>
       </c>
-      <c r="E121">
+      <c r="E121" t="n">
         <v>107643</v>
       </c>
-      <c r="F121">
+      <c r="F121" t="n">
         <v>3.7736788919999999E-5</v>
       </c>
-      <c r="G121">
+      <c r="G121" t="n">
         <v>1.132103667E-4</v>
       </c>
       <c r="H121" t="s">
@@ -4345,26 +4521,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122">
       <c r="A122" t="s">
         <v>40</v>
       </c>
-      <c r="B122">
+      <c r="B122" t="n">
         <v>2019</v>
       </c>
-      <c r="C122">
+      <c r="C122" t="n">
         <v>1</v>
       </c>
       <c r="D122" t="s">
         <v>29</v>
       </c>
-      <c r="E122">
+      <c r="E122" t="n">
         <v>107677</v>
       </c>
-      <c r="F122">
+      <c r="F122" t="n">
         <v>4.3397307250000002E-4</v>
       </c>
-      <c r="G122">
+      <c r="G122" t="n">
         <v>2.830259169E-4</v>
       </c>
       <c r="H122" t="s">
@@ -4374,26 +4550,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123">
       <c r="A123" t="s">
         <v>40</v>
       </c>
-      <c r="B123">
+      <c r="B123" t="n">
         <v>2019</v>
       </c>
-      <c r="C123">
+      <c r="C123" t="n">
         <v>1</v>
       </c>
       <c r="D123" t="s">
         <v>29</v>
       </c>
-      <c r="E123">
+      <c r="E123" t="n">
         <v>117302</v>
       </c>
-      <c r="F123">
+      <c r="F123" t="n">
         <v>1.8868394459999999E-5</v>
       </c>
-      <c r="G123">
+      <c r="G123" t="n">
         <v>1.8868394459999999E-5</v>
       </c>
       <c r="H123" t="s">
@@ -4403,26 +4579,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124">
       <c r="A124" t="s">
         <v>40</v>
       </c>
-      <c r="B124">
+      <c r="B124" t="n">
         <v>2019</v>
       </c>
-      <c r="C124">
+      <c r="C124" t="n">
         <v>1</v>
       </c>
       <c r="D124" t="s">
         <v>29</v>
       </c>
-      <c r="E124">
+      <c r="E124" t="n">
         <v>123867</v>
       </c>
-      <c r="F124">
+      <c r="F124" t="n">
         <v>1.320787612E-4</v>
       </c>
-      <c r="G124">
+      <c r="G124" t="n">
         <v>3.2076270579999998E-4</v>
       </c>
       <c r="H124" t="s">
@@ -4432,26 +4608,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125">
       <c r="A125" t="s">
         <v>40</v>
       </c>
-      <c r="B125">
+      <c r="B125" t="n">
         <v>2019</v>
       </c>
-      <c r="C125">
+      <c r="C125" t="n">
         <v>1</v>
       </c>
       <c r="D125" t="s">
         <v>29</v>
       </c>
-      <c r="E125">
+      <c r="E125" t="n">
         <v>123985</v>
       </c>
-      <c r="F125">
+      <c r="F125" t="n">
         <v>1.8868394459999999E-5</v>
       </c>
-      <c r="G125">
+      <c r="G125" t="n">
         <v>1.8868394460000001E-4</v>
       </c>
       <c r="H125" t="s">
@@ -4461,26 +4637,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126">
       <c r="A126" t="s">
         <v>40</v>
       </c>
-      <c r="B126">
+      <c r="B126" t="n">
         <v>2019</v>
       </c>
-      <c r="C126">
+      <c r="C126" t="n">
         <v>1</v>
       </c>
       <c r="D126" t="s">
         <v>29</v>
       </c>
-      <c r="E126">
+      <c r="E126" t="n">
         <v>124048</v>
       </c>
-      <c r="F126">
+      <c r="F126" t="n">
         <v>1.8868394459999999E-5</v>
       </c>
-      <c r="G126">
+      <c r="G126" t="n">
         <v>9.4341972290000001E-5</v>
       </c>
       <c r="H126" t="s">
@@ -4490,26 +4666,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127">
       <c r="A127" t="s">
         <v>40</v>
       </c>
-      <c r="B127">
+      <c r="B127" t="n">
         <v>2019</v>
       </c>
-      <c r="C127">
+      <c r="C127" t="n">
         <v>1</v>
       </c>
       <c r="D127" t="s">
         <v>29</v>
       </c>
-      <c r="E127">
+      <c r="E127" t="n">
         <v>124224</v>
       </c>
-      <c r="F127">
+      <c r="F127" t="n">
         <v>9.8115651179999991E-4</v>
       </c>
-      <c r="G127">
+      <c r="G127" t="n">
         <v>5.6605183370000002E-4</v>
       </c>
       <c r="H127" t="s">
@@ -4519,26 +4695,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128">
       <c r="A128" t="s">
         <v>40</v>
       </c>
-      <c r="B128">
+      <c r="B128" t="n">
         <v>2019</v>
       </c>
-      <c r="C128">
+      <c r="C128" t="n">
         <v>1</v>
       </c>
       <c r="D128" t="s">
         <v>29</v>
       </c>
-      <c r="E128">
+      <c r="E128" t="n">
         <v>124257</v>
       </c>
-      <c r="F128">
+      <c r="F128" t="n">
         <v>3.7736788919999999E-5</v>
       </c>
-      <c r="G128">
+      <c r="G128" t="n">
         <v>2.3585493069999998E-3</v>
       </c>
       <c r="H128" t="s">
@@ -4548,26 +4724,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129">
       <c r="A129" t="s">
         <v>40</v>
       </c>
-      <c r="B129">
+      <c r="B129" t="n">
         <v>2019</v>
       </c>
-      <c r="C129">
+      <c r="C129" t="n">
         <v>1</v>
       </c>
       <c r="D129" t="s">
         <v>29</v>
       </c>
-      <c r="E129">
+      <c r="E129" t="n">
         <v>124535</v>
       </c>
-      <c r="F129">
+      <c r="F129" t="n">
         <v>3.2076270579999998E-4</v>
       </c>
-      <c r="G129">
+      <c r="G129" t="n">
         <v>7.0869689580000006E-2</v>
       </c>
       <c r="H129" t="s">
@@ -4577,26 +4753,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130">
       <c r="A130" t="s">
         <v>40</v>
       </c>
-      <c r="B130">
+      <c r="B130" t="n">
         <v>2019</v>
       </c>
-      <c r="C130">
+      <c r="C130" t="n">
         <v>1</v>
       </c>
       <c r="D130" t="s">
         <v>29</v>
       </c>
-      <c r="E130">
+      <c r="E130" t="n">
         <v>124929</v>
       </c>
-      <c r="F130">
+      <c r="F130" t="n">
         <v>1.8868394459999999E-5</v>
       </c>
-      <c r="G130">
+      <c r="G130" t="n">
         <v>1.132103667E-4</v>
       </c>
       <c r="H130" t="s">
@@ -4606,26 +4782,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131">
       <c r="A131" t="s">
         <v>40</v>
       </c>
-      <c r="B131">
+      <c r="B131" t="n">
         <v>2019</v>
       </c>
-      <c r="C131">
+      <c r="C131" t="n">
         <v>1</v>
       </c>
       <c r="D131" t="s">
         <v>29</v>
       </c>
-      <c r="E131">
+      <c r="E131" t="n">
         <v>124951</v>
       </c>
-      <c r="F131">
+      <c r="F131" t="n">
         <v>1.8868394459999999E-5</v>
       </c>
-      <c r="G131">
+      <c r="G131" t="n">
         <v>5.6605183370000002E-5</v>
       </c>
       <c r="H131" t="s">
@@ -4635,26 +4811,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132">
       <c r="A132" t="s">
         <v>40</v>
       </c>
-      <c r="B132">
+      <c r="B132" t="n">
         <v>2019</v>
       </c>
-      <c r="C132">
+      <c r="C132" t="n">
         <v>1</v>
       </c>
       <c r="D132" t="s">
         <v>29</v>
       </c>
-      <c r="E132">
+      <c r="E132" t="n">
         <v>125131</v>
       </c>
-      <c r="F132">
+      <c r="F132" t="n">
         <v>5.6605183370000002E-5</v>
       </c>
-      <c r="G132">
+      <c r="G132" t="n">
         <v>3.7736788919999999E-5</v>
       </c>
       <c r="H132" t="s">
@@ -4664,26 +4840,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133">
       <c r="A133" t="s">
         <v>40</v>
       </c>
-      <c r="B133">
+      <c r="B133" t="n">
         <v>2019</v>
       </c>
-      <c r="C133">
+      <c r="C133" t="n">
         <v>1</v>
       </c>
       <c r="D133" t="s">
         <v>29</v>
       </c>
-      <c r="E133">
+      <c r="E133" t="n">
         <v>128506</v>
       </c>
-      <c r="F133">
+      <c r="F133" t="n">
         <v>1.8868394459999999E-5</v>
       </c>
-      <c r="G133">
+      <c r="G133" t="n">
         <v>3.7736788919999999E-5</v>
       </c>
       <c r="H133" t="s">
@@ -4693,26 +4869,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134">
       <c r="A134" t="s">
         <v>40</v>
       </c>
-      <c r="B134">
+      <c r="B134" t="n">
         <v>2019</v>
       </c>
-      <c r="C134">
+      <c r="C134" t="n">
         <v>1</v>
       </c>
       <c r="D134" t="s">
         <v>29</v>
       </c>
-      <c r="E134">
+      <c r="E134" t="n">
         <v>139024</v>
       </c>
-      <c r="F134">
+      <c r="F134" t="n">
         <v>3.7736788919999999E-5</v>
       </c>
-      <c r="G134">
+      <c r="G134" t="n">
         <v>1.698155501E-3</v>
       </c>
       <c r="H134" t="s">
@@ -4722,26 +4898,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135">
       <c r="A135" t="s">
         <v>40</v>
       </c>
-      <c r="B135">
+      <c r="B135" t="n">
         <v>2019</v>
       </c>
-      <c r="C135">
+      <c r="C135" t="n">
         <v>1</v>
       </c>
       <c r="D135" t="s">
         <v>29</v>
       </c>
-      <c r="E135">
+      <c r="E135" t="n">
         <v>139488</v>
       </c>
-      <c r="F135">
+      <c r="F135" t="n">
         <v>3.7736788919999999E-5</v>
       </c>
-      <c r="G135">
+      <c r="G135" t="n">
         <v>9.4341972290000001E-5</v>
       </c>
       <c r="H135" t="s">
@@ -4751,26 +4927,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136">
       <c r="A136" t="s">
         <v>40</v>
       </c>
-      <c r="B136">
+      <c r="B136" t="n">
         <v>2019</v>
       </c>
-      <c r="C136">
+      <c r="C136" t="n">
         <v>1</v>
       </c>
       <c r="D136" t="s">
         <v>29</v>
       </c>
-      <c r="E136">
+      <c r="E136" t="n">
         <v>532031</v>
       </c>
-      <c r="F136">
+      <c r="F136" t="n">
         <v>5.8492022819999997E-4</v>
       </c>
-      <c r="G136">
+      <c r="G136" t="n">
         <v>2.9830931639999999E-2</v>
       </c>
       <c r="H136" t="s">
@@ -4780,26 +4956,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137">
       <c r="A137" t="s">
         <v>40</v>
       </c>
-      <c r="B137">
+      <c r="B137" t="n">
         <v>2020</v>
       </c>
-      <c r="C137">
+      <c r="C137" t="n">
         <v>1</v>
       </c>
       <c r="D137" t="s">
         <v>29</v>
       </c>
-      <c r="E137">
+      <c r="E137" t="n">
         <v>100930</v>
       </c>
-      <c r="F137">
+      <c r="F137" t="n">
         <v>3.9309767650000003E-5</v>
       </c>
-      <c r="G137">
+      <c r="G137" t="n">
         <v>3.6164986239999998E-3</v>
       </c>
       <c r="H137" t="s">
@@ -4809,26 +4985,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138">
       <c r="A138" t="s">
         <v>40</v>
       </c>
-      <c r="B138">
+      <c r="B138" t="n">
         <v>2020</v>
       </c>
-      <c r="C138">
+      <c r="C138" t="n">
         <v>1</v>
       </c>
       <c r="D138" t="s">
         <v>29</v>
       </c>
-      <c r="E138">
+      <c r="E138" t="n">
         <v>100931</v>
       </c>
-      <c r="F138">
+      <c r="F138" t="n">
         <v>2.9482325740000002E-3</v>
       </c>
-      <c r="G138">
+      <c r="G138" t="n">
         <v>5.8964651480000003E-3</v>
       </c>
       <c r="H138" t="s">
@@ -4838,26 +5014,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139">
       <c r="A139" t="s">
         <v>40</v>
       </c>
-      <c r="B139">
+      <c r="B139" t="n">
         <v>2020</v>
       </c>
-      <c r="C139">
+      <c r="C139" t="n">
         <v>1</v>
       </c>
       <c r="D139" t="s">
         <v>29</v>
       </c>
-      <c r="E139">
+      <c r="E139" t="n">
         <v>107230</v>
       </c>
-      <c r="F139">
+      <c r="F139" t="n">
         <v>5.8964651479999999E-5</v>
       </c>
-      <c r="G139">
+      <c r="G139" t="n">
         <v>2.3585860589999999E-4</v>
       </c>
       <c r="H139" t="s">
@@ -4867,26 +5043,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140">
       <c r="A140" t="s">
         <v>40</v>
       </c>
-      <c r="B140">
+      <c r="B140" t="n">
         <v>2020</v>
       </c>
-      <c r="C140">
+      <c r="C140" t="n">
         <v>1</v>
       </c>
       <c r="D140" t="s">
         <v>29</v>
       </c>
-      <c r="E140">
+      <c r="E140" t="n">
         <v>107239</v>
       </c>
-      <c r="F140">
+      <c r="F140" t="n">
         <v>1.493771171E-3</v>
       </c>
-      <c r="G140">
+      <c r="G140" t="n">
         <v>1.1792930300000001E-2</v>
       </c>
       <c r="H140" t="s">
@@ -4896,26 +5072,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141">
       <c r="A141" t="s">
         <v>40</v>
       </c>
-      <c r="B141">
+      <c r="B141" t="n">
         <v>2020</v>
       </c>
-      <c r="C141">
+      <c r="C141" t="n">
         <v>1</v>
       </c>
       <c r="D141" t="s">
         <v>29</v>
       </c>
-      <c r="E141">
+      <c r="E141" t="n">
         <v>107254</v>
       </c>
-      <c r="F141">
+      <c r="F141" t="n">
         <v>2.5551348970000002E-4</v>
       </c>
-      <c r="G141">
+      <c r="G141" t="n">
         <v>2.1423823370000001E-2</v>
       </c>
       <c r="H141" t="s">
@@ -4925,26 +5101,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142">
       <c r="A142" t="s">
         <v>40</v>
       </c>
-      <c r="B142">
+      <c r="B142" t="n">
         <v>2020</v>
       </c>
-      <c r="C142">
+      <c r="C142" t="n">
         <v>1</v>
       </c>
       <c r="D142" t="s">
         <v>29</v>
       </c>
-      <c r="E142">
+      <c r="E142" t="n">
         <v>107558</v>
       </c>
-      <c r="F142">
+      <c r="F142" t="n">
         <v>1.965488383E-5</v>
       </c>
-      <c r="G142">
+      <c r="G142" t="n">
         <v>1.965488383E-5</v>
       </c>
       <c r="H142" t="s">
@@ -4954,26 +5130,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143">
       <c r="A143" t="s">
         <v>40</v>
       </c>
-      <c r="B143">
+      <c r="B143" t="n">
         <v>2020</v>
       </c>
-      <c r="C143">
+      <c r="C143" t="n">
         <v>1</v>
       </c>
       <c r="D143" t="s">
         <v>29</v>
       </c>
-      <c r="E143">
+      <c r="E143" t="n">
         <v>107643</v>
       </c>
-      <c r="F143">
+      <c r="F143" t="n">
         <v>1.965488383E-5</v>
       </c>
-      <c r="G143">
+      <c r="G143" t="n">
         <v>5.8964651479999999E-5</v>
       </c>
       <c r="H143" t="s">
@@ -4983,26 +5159,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144">
       <c r="A144" t="s">
         <v>40</v>
       </c>
-      <c r="B144">
+      <c r="B144" t="n">
         <v>2020</v>
       </c>
-      <c r="C144">
+      <c r="C144" t="n">
         <v>1</v>
       </c>
       <c r="D144" t="s">
         <v>29</v>
       </c>
-      <c r="E144">
+      <c r="E144" t="n">
         <v>107677</v>
       </c>
-      <c r="F144">
+      <c r="F144" t="n">
         <v>3.9309767650000003E-5</v>
       </c>
-      <c r="G144">
+      <c r="G144" t="n">
         <v>5.8964651479999999E-5</v>
       </c>
       <c r="H144" t="s">
@@ -5012,26 +5188,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145">
       <c r="A145" t="s">
         <v>40</v>
       </c>
-      <c r="B145">
+      <c r="B145" t="n">
         <v>2020</v>
       </c>
-      <c r="C145">
+      <c r="C145" t="n">
         <v>1</v>
       </c>
       <c r="D145" t="s">
         <v>29</v>
       </c>
-      <c r="E145">
+      <c r="E145" t="n">
         <v>107696</v>
       </c>
-      <c r="F145">
+      <c r="F145" t="n">
         <v>1.965488383E-5</v>
       </c>
-      <c r="G145">
+      <c r="G145" t="n">
         <v>3.9309767650000003E-5</v>
       </c>
       <c r="H145" t="s">
@@ -5041,26 +5217,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146">
       <c r="A146" t="s">
         <v>40</v>
       </c>
-      <c r="B146">
+      <c r="B146" t="n">
         <v>2020</v>
       </c>
-      <c r="C146">
+      <c r="C146" t="n">
         <v>1</v>
       </c>
       <c r="D146" t="s">
         <v>29</v>
       </c>
-      <c r="E146">
+      <c r="E146" t="n">
         <v>123867</v>
       </c>
-      <c r="F146">
+      <c r="F146" t="n">
         <v>3.9309767650000003E-5</v>
       </c>
-      <c r="G146">
+      <c r="G146" t="n">
         <v>2.1620372210000001E-4</v>
       </c>
       <c r="H146" t="s">
@@ -5070,26 +5246,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147">
       <c r="A147" t="s">
         <v>40</v>
       </c>
-      <c r="B147">
+      <c r="B147" t="n">
         <v>2020</v>
       </c>
-      <c r="C147">
+      <c r="C147" t="n">
         <v>1</v>
       </c>
       <c r="D147" t="s">
         <v>29</v>
       </c>
-      <c r="E147">
+      <c r="E147" t="n">
         <v>124224</v>
       </c>
-      <c r="F147">
+      <c r="F147" t="n">
         <v>1.965488383E-5</v>
       </c>
-      <c r="G147">
+      <c r="G147" t="n">
         <v>1.965488383E-5</v>
       </c>
       <c r="H147" t="s">
@@ -5099,26 +5275,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148">
       <c r="A148" t="s">
         <v>40</v>
       </c>
-      <c r="B148">
+      <c r="B148" t="n">
         <v>2020</v>
       </c>
-      <c r="C148">
+      <c r="C148" t="n">
         <v>1</v>
       </c>
       <c r="D148" t="s">
         <v>29</v>
       </c>
-      <c r="E148">
+      <c r="E148" t="n">
         <v>124535</v>
       </c>
-      <c r="F148">
+      <c r="F148" t="n">
         <v>2.9482325740000002E-4</v>
       </c>
-      <c r="G148">
+      <c r="G148" t="n">
         <v>4.2061451389999997E-2</v>
       </c>
       <c r="H148" t="s">
@@ -5128,26 +5304,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149">
       <c r="A149" t="s">
         <v>40</v>
       </c>
-      <c r="B149">
+      <c r="B149" t="n">
         <v>2020</v>
       </c>
-      <c r="C149">
+      <c r="C149" t="n">
         <v>1</v>
       </c>
       <c r="D149" t="s">
         <v>29</v>
       </c>
-      <c r="E149">
+      <c r="E149" t="n">
         <v>124929</v>
       </c>
-      <c r="F149">
+      <c r="F149" t="n">
         <v>3.9309767650000003E-5</v>
       </c>
-      <c r="G149">
+      <c r="G149" t="n">
         <v>2.3585860589999999E-4</v>
       </c>
       <c r="H149" t="s">
@@ -5157,26 +5333,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150">
       <c r="A150" t="s">
         <v>40</v>
       </c>
-      <c r="B150">
+      <c r="B150" t="n">
         <v>2020</v>
       </c>
-      <c r="C150">
+      <c r="C150" t="n">
         <v>1</v>
       </c>
       <c r="D150" t="s">
         <v>29</v>
       </c>
-      <c r="E150">
+      <c r="E150" t="n">
         <v>138899</v>
       </c>
-      <c r="F150">
+      <c r="F150" t="n">
         <v>3.9309767650000003E-5</v>
       </c>
-      <c r="G150">
+      <c r="G150" t="n">
         <v>5.6999163100000002E-4</v>
       </c>
       <c r="H150" t="s">
@@ -5186,26 +5362,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151">
       <c r="A151" t="s">
         <v>40</v>
       </c>
-      <c r="B151">
+      <c r="B151" t="n">
         <v>2020</v>
       </c>
-      <c r="C151">
+      <c r="C151" t="n">
         <v>1</v>
       </c>
       <c r="D151" t="s">
         <v>29</v>
       </c>
-      <c r="E151">
+      <c r="E151" t="n">
         <v>139488</v>
       </c>
-      <c r="F151">
+      <c r="F151" t="n">
         <v>1.965488383E-5</v>
       </c>
-      <c r="G151">
+      <c r="G151" t="n">
         <v>3.9309767650000003E-5</v>
       </c>
       <c r="H151" t="s">
@@ -5215,26 +5391,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152">
       <c r="A152" t="s">
         <v>40</v>
       </c>
-      <c r="B152">
+      <c r="B152" t="n">
         <v>2020</v>
       </c>
-      <c r="C152">
+      <c r="C152" t="n">
         <v>1</v>
       </c>
       <c r="D152" t="s">
         <v>29</v>
       </c>
-      <c r="E152">
+      <c r="E152" t="n">
         <v>532031</v>
       </c>
-      <c r="F152">
+      <c r="F152" t="n">
         <v>2.0244530340000001E-3</v>
       </c>
-      <c r="G152">
+      <c r="G152" t="n">
         <v>2.7123739680000002E-2</v>
       </c>
       <c r="H152" t="s">
@@ -5244,26 +5420,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153">
       <c r="A153" t="s">
         <v>40</v>
       </c>
-      <c r="B153">
+      <c r="B153" t="n">
         <v>2021</v>
       </c>
-      <c r="C153">
+      <c r="C153" t="n">
         <v>1</v>
       </c>
       <c r="D153" t="s">
         <v>29</v>
       </c>
-      <c r="E153">
+      <c r="E153" t="n">
         <v>100930</v>
       </c>
-      <c r="F153">
+      <c r="F153" t="n">
         <v>5.7595989479999997E-5</v>
       </c>
-      <c r="G153">
+      <c r="G153" t="n">
         <v>3.1101834319999999E-3</v>
       </c>
       <c r="H153" t="s">
@@ -5273,26 +5449,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154">
       <c r="A154" t="s">
         <v>40</v>
       </c>
-      <c r="B154">
+      <c r="B154" t="n">
         <v>2021</v>
       </c>
-      <c r="C154">
+      <c r="C154" t="n">
         <v>1</v>
       </c>
       <c r="D154" t="s">
         <v>29</v>
       </c>
-      <c r="E154">
+      <c r="E154" t="n">
         <v>107230</v>
       </c>
-      <c r="F154">
+      <c r="F154" t="n">
         <v>1.9198663159999999E-5</v>
       </c>
-      <c r="G154">
+      <c r="G154" t="n">
         <v>9.5993315789999999E-5</v>
       </c>
       <c r="H154" t="s">
@@ -5302,26 +5478,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155">
       <c r="A155" t="s">
         <v>40</v>
       </c>
-      <c r="B155">
+      <c r="B155" t="n">
         <v>2021</v>
       </c>
-      <c r="C155">
+      <c r="C155" t="n">
         <v>1</v>
       </c>
       <c r="D155" t="s">
         <v>29</v>
       </c>
-      <c r="E155">
+      <c r="E155" t="n">
         <v>107254</v>
       </c>
-      <c r="F155">
+      <c r="F155" t="n">
         <v>7.6794652630000006E-5</v>
       </c>
-      <c r="G155">
+      <c r="G155" t="n">
         <v>3.321368726E-3</v>
       </c>
       <c r="H155" t="s">
@@ -5331,26 +5507,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156">
       <c r="A156" t="s">
         <v>40</v>
       </c>
-      <c r="B156">
+      <c r="B156" t="n">
         <v>2021</v>
       </c>
-      <c r="C156">
+      <c r="C156" t="n">
         <v>1</v>
       </c>
       <c r="D156" t="s">
         <v>29</v>
       </c>
-      <c r="E156">
+      <c r="E156" t="n">
         <v>107292</v>
       </c>
-      <c r="F156">
+      <c r="F156" t="n">
         <v>1.9198663159999999E-5</v>
       </c>
-      <c r="G156">
+      <c r="G156" t="n">
         <v>3.8397326319999998E-5</v>
       </c>
       <c r="H156" t="s">
@@ -5360,26 +5536,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157">
       <c r="A157" t="s">
         <v>40</v>
       </c>
-      <c r="B157">
+      <c r="B157" t="n">
         <v>2021</v>
       </c>
-      <c r="C157">
+      <c r="C157" t="n">
         <v>1</v>
       </c>
       <c r="D157" t="s">
         <v>29</v>
       </c>
-      <c r="E157">
+      <c r="E157" t="n">
         <v>107643</v>
       </c>
-      <c r="F157">
+      <c r="F157" t="n">
         <v>1.9198663159999999E-5</v>
       </c>
-      <c r="G157">
+      <c r="G157" t="n">
         <v>3.8397326319999998E-5</v>
       </c>
       <c r="H157" t="s">
@@ -5389,26 +5565,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158">
       <c r="A158" t="s">
         <v>40</v>
       </c>
-      <c r="B158">
+      <c r="B158" t="n">
         <v>2021</v>
       </c>
-      <c r="C158">
+      <c r="C158" t="n">
         <v>1</v>
       </c>
       <c r="D158" t="s">
         <v>29</v>
       </c>
-      <c r="E158">
+      <c r="E158" t="n">
         <v>107677</v>
       </c>
-      <c r="F158">
+      <c r="F158" t="n">
         <v>5.7595989479999997E-5</v>
       </c>
-      <c r="G158">
+      <c r="G158" t="n">
         <v>9.5993315789999999E-5</v>
       </c>
       <c r="H158" t="s">
@@ -5418,26 +5594,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159">
       <c r="A159" t="s">
         <v>40</v>
       </c>
-      <c r="B159">
+      <c r="B159" t="n">
         <v>2021</v>
       </c>
-      <c r="C159">
+      <c r="C159" t="n">
         <v>1</v>
       </c>
       <c r="D159" t="s">
         <v>29</v>
       </c>
-      <c r="E159">
+      <c r="E159" t="n">
         <v>123851</v>
       </c>
-      <c r="F159">
+      <c r="F159" t="n">
         <v>5.7595989479999997E-5</v>
       </c>
-      <c r="G159">
+      <c r="G159" t="n">
         <v>2.8797994739999998E-4</v>
       </c>
       <c r="H159" t="s">
@@ -5447,26 +5623,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160">
       <c r="A160" t="s">
         <v>40</v>
       </c>
-      <c r="B160">
+      <c r="B160" t="n">
         <v>2021</v>
       </c>
-      <c r="C160">
+      <c r="C160" t="n">
         <v>1</v>
       </c>
       <c r="D160" t="s">
         <v>29</v>
       </c>
-      <c r="E160">
+      <c r="E160" t="n">
         <v>123908</v>
       </c>
-      <c r="F160">
+      <c r="F160" t="n">
         <v>3.8397326319999998E-5</v>
       </c>
-      <c r="G160">
+      <c r="G160" t="n">
         <v>9.2153583160000004E-4</v>
       </c>
       <c r="H160" t="s">
@@ -5476,26 +5652,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161">
       <c r="A161" t="s">
         <v>40</v>
       </c>
-      <c r="B161">
+      <c r="B161" t="n">
         <v>2021</v>
       </c>
-      <c r="C161">
+      <c r="C161" t="n">
         <v>1</v>
       </c>
       <c r="D161" t="s">
         <v>29</v>
       </c>
-      <c r="E161">
+      <c r="E161" t="n">
         <v>124048</v>
       </c>
-      <c r="F161">
+      <c r="F161" t="n">
         <v>3.8397326319999998E-5</v>
       </c>
-      <c r="G161">
+      <c r="G161" t="n">
         <v>6.9115187370000003E-4</v>
       </c>
       <c r="H161" t="s">
@@ -5505,26 +5681,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162">
       <c r="A162" t="s">
         <v>40</v>
       </c>
-      <c r="B162">
+      <c r="B162" t="n">
         <v>2021</v>
       </c>
-      <c r="C162">
+      <c r="C162" t="n">
         <v>1</v>
       </c>
       <c r="D162" t="s">
         <v>29</v>
       </c>
-      <c r="E162">
+      <c r="E162" t="n">
         <v>124257</v>
       </c>
-      <c r="F162">
+      <c r="F162" t="n">
         <v>1.9198663159999999E-5</v>
       </c>
-      <c r="G162">
+      <c r="G162" t="n">
         <v>3.8397326320000001E-4</v>
       </c>
       <c r="H162" t="s">
@@ -5534,26 +5710,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163">
       <c r="A163" t="s">
         <v>40</v>
       </c>
-      <c r="B163">
+      <c r="B163" t="n">
         <v>2021</v>
       </c>
-      <c r="C163">
+      <c r="C163" t="n">
         <v>1</v>
       </c>
       <c r="D163" t="s">
         <v>29</v>
       </c>
-      <c r="E163">
+      <c r="E163" t="n">
         <v>124343</v>
       </c>
-      <c r="F163">
+      <c r="F163" t="n">
         <v>1.9198663159999999E-5</v>
       </c>
-      <c r="G163">
+      <c r="G163" t="n">
         <v>5.7595989479999997E-5</v>
       </c>
       <c r="H163" t="s">
@@ -5563,26 +5739,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164">
       <c r="A164" t="s">
         <v>40</v>
       </c>
-      <c r="B164">
+      <c r="B164" t="n">
         <v>2021</v>
       </c>
-      <c r="C164">
+      <c r="C164" t="n">
         <v>1</v>
       </c>
       <c r="D164" t="s">
         <v>29</v>
       </c>
-      <c r="E164">
+      <c r="E164" t="n">
         <v>124535</v>
       </c>
-      <c r="F164">
+      <c r="F164" t="n">
         <v>5.7595989479999997E-5</v>
       </c>
-      <c r="G164">
+      <c r="G164" t="n">
         <v>1.3055090950000001E-2</v>
       </c>
       <c r="H164" t="s">
@@ -5592,26 +5768,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165">
       <c r="A165" t="s">
         <v>40</v>
       </c>
-      <c r="B165">
+      <c r="B165" t="n">
         <v>2021</v>
       </c>
-      <c r="C165">
+      <c r="C165" t="n">
         <v>1</v>
       </c>
       <c r="D165" t="s">
         <v>29</v>
       </c>
-      <c r="E165">
+      <c r="E165" t="n">
         <v>138930</v>
       </c>
-      <c r="F165">
+      <c r="F165" t="n">
         <v>1.9198663159999999E-5</v>
       </c>
-      <c r="G165">
+      <c r="G165" t="n">
         <v>9.5993315789999999E-5</v>
       </c>
       <c r="H165" t="s">
@@ -5621,26 +5797,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166">
       <c r="A166" t="s">
         <v>40</v>
       </c>
-      <c r="B166">
+      <c r="B166" t="n">
         <v>2021</v>
       </c>
-      <c r="C166">
+      <c r="C166" t="n">
         <v>1</v>
       </c>
       <c r="D166" t="s">
         <v>29</v>
       </c>
-      <c r="E166">
+      <c r="E166" t="n">
         <v>149898</v>
       </c>
-      <c r="F166">
+      <c r="F166" t="n">
         <v>3.8397326319999998E-5</v>
       </c>
-      <c r="G166">
+      <c r="G166" t="n">
         <v>5.9515855790000004E-3</v>
       </c>
       <c r="H166" t="s">
@@ -5650,26 +5826,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167">
       <c r="A167" t="s">
         <v>40</v>
       </c>
-      <c r="B167">
+      <c r="B167" t="n">
         <v>2021</v>
       </c>
-      <c r="C167">
+      <c r="C167" t="n">
         <v>1</v>
       </c>
       <c r="D167" t="s">
         <v>29</v>
       </c>
-      <c r="E167">
+      <c r="E167" t="n">
         <v>532031</v>
       </c>
-      <c r="F167">
+      <c r="F167" t="n">
         <v>9.5993315789999999E-5</v>
       </c>
-      <c r="G167">
+      <c r="G167" t="n">
         <v>1.8430716629999999E-3</v>
       </c>
       <c r="H167" t="s">
@@ -5679,26 +5855,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168">
       <c r="A168" t="s">
         <v>40</v>
       </c>
-      <c r="B168">
+      <c r="B168" t="n">
         <v>2022</v>
       </c>
-      <c r="C168">
+      <c r="C168" t="n">
         <v>1</v>
       </c>
       <c r="D168" t="s">
         <v>29</v>
       </c>
-      <c r="E168">
+      <c r="E168" t="n">
         <v>107120</v>
       </c>
-      <c r="F168">
+      <c r="F168" t="n">
         <v>3.876610586E-5</v>
       </c>
-      <c r="G168">
+      <c r="G168" t="n">
         <v>7.7532211730000004E-5</v>
       </c>
       <c r="H168" t="s">
@@ -5708,26 +5884,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169">
       <c r="A169" t="s">
         <v>40</v>
       </c>
-      <c r="B169">
+      <c r="B169" t="n">
         <v>2022</v>
       </c>
-      <c r="C169">
+      <c r="C169" t="n">
         <v>1</v>
       </c>
       <c r="D169" t="s">
         <v>29</v>
       </c>
-      <c r="E169">
+      <c r="E169" t="n">
         <v>107230</v>
       </c>
-      <c r="F169">
+      <c r="F169" t="n">
         <v>1.162983176E-4</v>
       </c>
-      <c r="G169">
+      <c r="G169" t="n">
         <v>3.4889495280000001E-4</v>
       </c>
       <c r="H169" t="s">
@@ -5737,26 +5913,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170">
       <c r="A170" t="s">
         <v>40</v>
       </c>
-      <c r="B170">
+      <c r="B170" t="n">
         <v>2022</v>
       </c>
-      <c r="C170">
+      <c r="C170" t="n">
         <v>1</v>
       </c>
       <c r="D170" t="s">
         <v>29</v>
       </c>
-      <c r="E170">
+      <c r="E170" t="n">
         <v>107254</v>
       </c>
-      <c r="F170">
+      <c r="F170" t="n">
         <v>7.3655601139999995E-4</v>
       </c>
-      <c r="G170">
+      <c r="G170" t="n">
         <v>8.6157670280000001E-2</v>
       </c>
       <c r="H170" t="s">
@@ -5766,26 +5942,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171">
       <c r="A171" t="s">
         <v>40</v>
       </c>
-      <c r="B171">
+      <c r="B171" t="n">
         <v>2022</v>
       </c>
-      <c r="C171">
+      <c r="C171" t="n">
         <v>1</v>
       </c>
       <c r="D171" t="s">
         <v>29</v>
       </c>
-      <c r="E171">
+      <c r="E171" t="n">
         <v>107292</v>
       </c>
-      <c r="F171">
+      <c r="F171" t="n">
         <v>1.356813705E-4</v>
       </c>
-      <c r="G171">
+      <c r="G171" t="n">
         <v>2.325966352E-4</v>
       </c>
       <c r="H171" t="s">
@@ -5795,26 +5971,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172">
       <c r="A172" t="s">
         <v>40</v>
       </c>
-      <c r="B172">
+      <c r="B172" t="n">
         <v>2022</v>
       </c>
-      <c r="C172">
+      <c r="C172" t="n">
         <v>1</v>
       </c>
       <c r="D172" t="s">
         <v>29</v>
       </c>
-      <c r="E172">
+      <c r="E172" t="n">
         <v>107342</v>
       </c>
-      <c r="F172">
+      <c r="F172" t="n">
         <v>3.876610586E-5</v>
       </c>
-      <c r="G172">
+      <c r="G172" t="n">
         <v>3.876610586E-5</v>
       </c>
       <c r="H172" t="s">
@@ -5824,26 +6000,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173">
       <c r="A173" t="s">
         <v>40</v>
       </c>
-      <c r="B173">
+      <c r="B173" t="n">
         <v>2022</v>
       </c>
-      <c r="C173">
+      <c r="C173" t="n">
         <v>1</v>
       </c>
       <c r="D173" t="s">
         <v>29</v>
       </c>
-      <c r="E173">
+      <c r="E173" t="n">
         <v>107558</v>
       </c>
-      <c r="F173">
+      <c r="F173" t="n">
         <v>1.938305293E-5</v>
       </c>
-      <c r="G173">
+      <c r="G173" t="n">
         <v>1.938305293E-5</v>
       </c>
       <c r="H173" t="s">
@@ -5853,26 +6029,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174">
       <c r="A174" t="s">
         <v>40</v>
       </c>
-      <c r="B174">
+      <c r="B174" t="n">
         <v>2022</v>
       </c>
-      <c r="C174">
+      <c r="C174" t="n">
         <v>1</v>
       </c>
       <c r="D174" t="s">
         <v>29</v>
       </c>
-      <c r="E174">
+      <c r="E174" t="n">
         <v>107564</v>
       </c>
-      <c r="F174">
+      <c r="F174" t="n">
         <v>1.938305293E-5</v>
       </c>
-      <c r="G174">
+      <c r="G174" t="n">
         <v>1.938305293E-5</v>
       </c>
       <c r="H174" t="s">
@@ -5882,26 +6058,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175">
       <c r="A175" t="s">
         <v>40</v>
       </c>
-      <c r="B175">
+      <c r="B175" t="n">
         <v>2022</v>
       </c>
-      <c r="C175">
+      <c r="C175" t="n">
         <v>1</v>
       </c>
       <c r="D175" t="s">
         <v>29</v>
       </c>
-      <c r="E175">
+      <c r="E175" t="n">
         <v>107643</v>
       </c>
-      <c r="F175">
+      <c r="F175" t="n">
         <v>1.162983176E-4</v>
       </c>
-      <c r="G175">
+      <c r="G175" t="n">
         <v>4.0704411159999998E-4</v>
       </c>
       <c r="H175" t="s">
@@ -5911,26 +6087,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176">
       <c r="A176" t="s">
         <v>40</v>
       </c>
-      <c r="B176">
+      <c r="B176" t="n">
         <v>2022</v>
       </c>
-      <c r="C176">
+      <c r="C176" t="n">
         <v>1</v>
       </c>
       <c r="D176" t="s">
         <v>29</v>
       </c>
-      <c r="E176">
+      <c r="E176" t="n">
         <v>107677</v>
       </c>
-      <c r="F176">
+      <c r="F176" t="n">
         <v>1.162983176E-4</v>
       </c>
-      <c r="G176">
+      <c r="G176" t="n">
         <v>1.162983176E-4</v>
       </c>
       <c r="H176" t="s">
@@ -5940,26 +6116,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177">
       <c r="A177" t="s">
         <v>40</v>
       </c>
-      <c r="B177">
+      <c r="B177" t="n">
         <v>2022</v>
       </c>
-      <c r="C177">
+      <c r="C177" t="n">
         <v>1</v>
       </c>
       <c r="D177" t="s">
         <v>29</v>
       </c>
-      <c r="E177">
+      <c r="E177" t="n">
         <v>123867</v>
       </c>
-      <c r="F177">
+      <c r="F177" t="n">
         <v>1.938305293E-5</v>
       </c>
-      <c r="G177">
+      <c r="G177" t="n">
         <v>3.876610586E-5</v>
       </c>
       <c r="H177" t="s">
@@ -5969,26 +6145,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178">
       <c r="A178" t="s">
         <v>40</v>
       </c>
-      <c r="B178">
+      <c r="B178" t="n">
         <v>2022</v>
       </c>
-      <c r="C178">
+      <c r="C178" t="n">
         <v>1</v>
       </c>
       <c r="D178" t="s">
         <v>29</v>
       </c>
-      <c r="E178">
+      <c r="E178" t="n">
         <v>124257</v>
       </c>
-      <c r="F178">
+      <c r="F178" t="n">
         <v>1.938305293E-5</v>
       </c>
-      <c r="G178">
+      <c r="G178" t="n">
         <v>1.2405153879999999E-3</v>
       </c>
       <c r="H178" t="s">
@@ -5998,26 +6174,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179">
       <c r="A179" t="s">
         <v>40</v>
       </c>
-      <c r="B179">
+      <c r="B179" t="n">
         <v>2022</v>
       </c>
-      <c r="C179">
+      <c r="C179" t="n">
         <v>1</v>
       </c>
       <c r="D179" t="s">
         <v>29</v>
       </c>
-      <c r="E179">
+      <c r="E179" t="n">
         <v>124535</v>
       </c>
-      <c r="F179">
+      <c r="F179" t="n">
         <v>5.8149158790000001E-4</v>
       </c>
-      <c r="G179">
+      <c r="G179" t="n">
         <v>5.2334242920000003E-2</v>
       </c>
       <c r="H179" t="s">
@@ -6027,26 +6203,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180">
       <c r="A180" t="s">
         <v>40</v>
       </c>
-      <c r="B180">
+      <c r="B180" t="n">
         <v>2022</v>
       </c>
-      <c r="C180">
+      <c r="C180" t="n">
         <v>1</v>
       </c>
       <c r="D180" t="s">
         <v>29</v>
       </c>
-      <c r="E180">
+      <c r="E180" t="n">
         <v>125131</v>
       </c>
-      <c r="F180">
+      <c r="F180" t="n">
         <v>1.938305293E-5</v>
       </c>
-      <c r="G180">
+      <c r="G180" t="n">
         <v>7.7532211730000004E-5</v>
       </c>
       <c r="H180" t="s">
@@ -6056,26 +6232,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181">
       <c r="A181" t="s">
         <v>40</v>
       </c>
-      <c r="B181">
+      <c r="B181" t="n">
         <v>2022</v>
       </c>
-      <c r="C181">
+      <c r="C181" t="n">
         <v>1</v>
       </c>
       <c r="D181" t="s">
         <v>29</v>
       </c>
-      <c r="E181">
+      <c r="E181" t="n">
         <v>131779</v>
       </c>
-      <c r="F181">
+      <c r="F181" t="n">
         <v>1.938305293E-5</v>
       </c>
-      <c r="G181">
+      <c r="G181" t="n">
         <v>4.651932704E-4</v>
       </c>
       <c r="H181" t="s">
@@ -6085,26 +6261,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182">
       <c r="A182" t="s">
         <v>40</v>
       </c>
-      <c r="B182">
+      <c r="B182" t="n">
         <v>2022</v>
       </c>
-      <c r="C182">
+      <c r="C182" t="n">
         <v>1</v>
       </c>
       <c r="D182" t="s">
         <v>29</v>
       </c>
-      <c r="E182">
+      <c r="E182" t="n">
         <v>138899</v>
       </c>
-      <c r="F182">
+      <c r="F182" t="n">
         <v>3.876610586E-5</v>
       </c>
-      <c r="G182">
+      <c r="G182" t="n">
         <v>3.2951189980000002E-4</v>
       </c>
       <c r="H182" t="s">
@@ -6114,26 +6290,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183">
       <c r="A183" t="s">
         <v>40</v>
       </c>
-      <c r="B183">
+      <c r="B183" t="n">
         <v>2022</v>
       </c>
-      <c r="C183">
+      <c r="C183" t="n">
         <v>1</v>
       </c>
       <c r="D183" t="s">
         <v>29</v>
       </c>
-      <c r="E183">
+      <c r="E183" t="n">
         <v>139024</v>
       </c>
-      <c r="F183">
+      <c r="F183" t="n">
         <v>3.876610586E-5</v>
       </c>
-      <c r="G183">
+      <c r="G183" t="n">
         <v>2.093369717E-3</v>
       </c>
       <c r="H183" t="s">
@@ -6143,26 +6319,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184">
       <c r="A184" t="s">
         <v>40</v>
       </c>
-      <c r="B184">
+      <c r="B184" t="n">
         <v>2022</v>
       </c>
-      <c r="C184">
+      <c r="C184" t="n">
         <v>1</v>
       </c>
       <c r="D184" t="s">
         <v>29</v>
       </c>
-      <c r="E184">
+      <c r="E184" t="n">
         <v>241154</v>
       </c>
-      <c r="F184">
+      <c r="F184" t="n">
         <v>1.938305293E-5</v>
       </c>
-      <c r="G184">
+      <c r="G184" t="n">
         <v>3.876610586E-5</v>
       </c>
       <c r="H184" t="s">
@@ -6172,26 +6348,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185">
       <c r="A185" t="s">
         <v>40</v>
       </c>
-      <c r="B185">
+      <c r="B185" t="n">
         <v>2022</v>
       </c>
-      <c r="C185">
+      <c r="C185" t="n">
         <v>1</v>
       </c>
       <c r="D185" t="s">
         <v>29</v>
       </c>
-      <c r="E185">
+      <c r="E185" t="n">
         <v>532031</v>
       </c>
-      <c r="F185">
+      <c r="F185" t="n">
         <v>1.2986645459999999E-3</v>
       </c>
-      <c r="G185">
+      <c r="G185" t="n">
         <v>9.0325026659999995E-3</v>
       </c>
       <c r="H185" t="s">
@@ -6208,665 +6384,806 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:S11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="19" max="19" width="11.42578125" style="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="E1" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="F1" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="G1" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="H1" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="I1" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="J1" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="K1" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="L1" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="M1" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="N1" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="O1" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="P1" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="Q1" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="R1" t="s">
-        <v>64</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="S1" t="s">
+        <v>108</v>
+      </c>
+      <c r="T1" t="s">
+        <v>109</v>
+      </c>
+      <c r="U1" t="s">
+        <v>110</v>
+      </c>
+      <c r="V1" t="s">
+        <v>111</v>
+      </c>
+      <c r="W1" t="s">
+        <v>112</v>
+      </c>
+      <c r="X1" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2">
+        <v>119</v>
+      </c>
+      <c r="D2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" t="n">
         <v>-4.993416667</v>
       </c>
-      <c r="E2">
-        <v>43.638249999999999</v>
-      </c>
-      <c r="F2">
+      <c r="F2" t="n">
+        <v>43.63825</v>
+      </c>
+      <c r="G2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J2"/>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>124</v>
+      </c>
+      <c r="M2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N2"/>
+      <c r="O2" t="n">
+        <v>1.27153199084637</v>
+      </c>
+      <c r="P2" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2" t="n">
+        <v>0.228001944566154</v>
+      </c>
+      <c r="T2" t="n">
+        <v>53930.22</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.15909447431823</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.03851272997037</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.04892723</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.41998243</v>
+      </c>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2" t="n">
+        <v>0.255817685800294</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-4.997333333</v>
+      </c>
+      <c r="F3" t="n">
+        <v>43.63633333</v>
+      </c>
+      <c r="G3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>124</v>
+      </c>
+      <c r="M3" t="s">
+        <v>125</v>
+      </c>
+      <c r="N3"/>
+      <c r="O3" t="n">
+        <v>3.11020394458587</v>
+      </c>
+      <c r="P3" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q3"/>
+      <c r="R3"/>
+      <c r="S3" t="n">
+        <v>0.0715028060805002</v>
+      </c>
+      <c r="T3" t="n">
+        <v>50085.14</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.12007553537452</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.09605643509777</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.85796488</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.87360566</v>
+      </c>
+      <c r="Y3"/>
+      <c r="Z3"/>
+      <c r="AA3" t="n">
+        <v>0.546317466911022</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-4.97125</v>
+      </c>
+      <c r="F4" t="n">
+        <v>43.63783333</v>
+      </c>
+      <c r="G4" t="s">
+        <v>121</v>
+      </c>
+      <c r="H4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>124</v>
+      </c>
+      <c r="M4" t="s">
+        <v>125</v>
+      </c>
+      <c r="N4"/>
+      <c r="O4" t="n">
+        <v>3.13328060654436</v>
+      </c>
+      <c r="P4" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q4"/>
+      <c r="R4"/>
+      <c r="S4" t="n">
+        <v>0.0978398983544962</v>
+      </c>
+      <c r="T4" t="n">
+        <v>55000.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.12894428232576</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.08590830992433</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.00681502</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.02983561</v>
+      </c>
+      <c r="Y4"/>
+      <c r="Z4"/>
+      <c r="AA4" t="n">
+        <v>0.569417989409479</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-4.997416667</v>
+      </c>
+      <c r="F5" t="n">
+        <v>43.63616667</v>
+      </c>
+      <c r="G5" t="s">
+        <v>121</v>
+      </c>
+      <c r="H5" t="s">
+        <v>122</v>
+      </c>
+      <c r="I5" t="s">
+        <v>123</v>
+      </c>
+      <c r="J5"/>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>124</v>
+      </c>
+      <c r="M5" t="s">
+        <v>125</v>
+      </c>
+      <c r="N5"/>
+      <c r="O5" t="n">
+        <v>0.46203778819068</v>
+      </c>
+      <c r="P5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="S5" t="n">
+        <v>0.218556701063</v>
+      </c>
+      <c r="T5" t="n">
+        <v>54584.28</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.03334293316614</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.01777068416118</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.97955493</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.10870807</v>
+      </c>
+      <c r="Y5"/>
+      <c r="Z5"/>
+      <c r="AA5" t="n">
+        <v>0.397938144332186</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-4.994416667</v>
+      </c>
+      <c r="F6" t="n">
+        <v>43.63675</v>
+      </c>
+      <c r="G6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I6" t="s">
+        <v>123</v>
+      </c>
+      <c r="J6"/>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>124</v>
+      </c>
+      <c r="M6" t="s">
+        <v>125</v>
+      </c>
+      <c r="N6"/>
+      <c r="O6" t="n">
+        <v>0.669539367814</v>
+      </c>
+      <c r="P6" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q6"/>
+      <c r="R6"/>
+      <c r="S6" t="n">
+        <v>0.499659632411678</v>
+      </c>
+      <c r="T6" t="n">
+        <v>55000.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.0449995909115</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.02670884810099</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.81638037</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.91049316</v>
+      </c>
+      <c r="Y6"/>
+      <c r="Z6"/>
+      <c r="AA6" t="n">
+        <v>0.47288404810933</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-4.990333333</v>
+      </c>
+      <c r="F7" t="n">
+        <v>43.63733333</v>
+      </c>
+      <c r="G7" t="s">
+        <v>121</v>
+      </c>
+      <c r="H7" t="s">
+        <v>142</v>
+      </c>
+      <c r="I7" t="s">
+        <v>123</v>
+      </c>
+      <c r="J7"/>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>124</v>
+      </c>
+      <c r="M7" t="s">
+        <v>125</v>
+      </c>
+      <c r="N7"/>
+      <c r="O7" t="n">
+        <v>0.70365366502812</v>
+      </c>
+      <c r="P7" t="n">
         <v>9</v>
       </c>
-      <c r="G2">
-        <v>387.86584470000003</v>
-      </c>
-      <c r="H2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2">
-        <v>53930.22</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L2" t="s">
-        <v>71</v>
-      </c>
-      <c r="M2">
-        <v>0.15909447431823001</v>
-      </c>
-      <c r="N2">
-        <v>3.8512729970370002E-2</v>
-      </c>
-      <c r="O2">
-        <v>1.27153199084637</v>
-      </c>
-      <c r="P2">
-        <v>27</v>
-      </c>
-      <c r="Q2">
-        <v>1.0489272300000001</v>
-      </c>
-      <c r="R2">
-        <v>1.4199824299999999</v>
-      </c>
-      <c r="S2" s="1">
-        <v>0.228001944566154</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3">
-        <v>-4.9973333330000003</v>
-      </c>
-      <c r="E3">
-        <v>43.636333329999999</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>387.86584470000003</v>
-      </c>
-      <c r="H3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3">
-        <v>50085.14</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
-        <v>70</v>
-      </c>
-      <c r="L3" t="s">
-        <v>71</v>
-      </c>
-      <c r="M3">
-        <v>0.12007553537452</v>
-      </c>
-      <c r="N3">
-        <v>9.6056435097769996E-2</v>
-      </c>
-      <c r="O3">
-        <v>3.1102039445858698</v>
-      </c>
-      <c r="P3">
+      <c r="Q7"/>
+      <c r="R7"/>
+      <c r="S7" t="n">
+        <v>0.793769470419342</v>
+      </c>
+      <c r="T7" t="n">
+        <v>54742.84</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.01841336693424</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.05863780541901</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.45759724</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.39180368</v>
+      </c>
+      <c r="Y7"/>
+      <c r="Z7"/>
+      <c r="AA7" t="n">
+        <v>0.291173416410489</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-4.993583333</v>
+      </c>
+      <c r="F8" t="n">
+        <v>43.637</v>
+      </c>
+      <c r="G8" t="s">
+        <v>121</v>
+      </c>
+      <c r="H8" t="s">
+        <v>122</v>
+      </c>
+      <c r="I8" t="s">
+        <v>123</v>
+      </c>
+      <c r="J8"/>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
+        <v>124</v>
+      </c>
+      <c r="M8" t="s">
+        <v>125</v>
+      </c>
+      <c r="N8"/>
+      <c r="O8" t="n">
+        <v>4.09085660239938</v>
+      </c>
+      <c r="P8" t="n">
         <v>21</v>
       </c>
-      <c r="Q3">
-        <v>0.85796488000000004</v>
-      </c>
-      <c r="R3">
-        <v>0.87360565999999995</v>
-      </c>
-      <c r="S3" s="1">
-        <v>7.1502806080500206E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4">
-        <v>-4.9712500000000004</v>
-      </c>
-      <c r="E4">
-        <v>43.637833329999999</v>
-      </c>
-      <c r="F4">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>420.2323303</v>
-      </c>
-      <c r="H4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4">
-        <v>55000.5</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L4" t="s">
-        <v>71</v>
-      </c>
-      <c r="M4">
-        <v>0.12894428232576</v>
-      </c>
-      <c r="N4">
-        <v>8.5908309924330004E-2</v>
-      </c>
-      <c r="O4">
-        <v>3.1332806065443601</v>
-      </c>
-      <c r="P4">
-        <v>24</v>
-      </c>
-      <c r="Q4">
-        <v>1.0068150199999999</v>
-      </c>
-      <c r="R4">
-        <v>1.0298356099999999</v>
-      </c>
-      <c r="S4" s="1">
-        <v>9.7839898354496205E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5">
-        <v>-4.9974166670000004</v>
-      </c>
-      <c r="E5">
-        <v>43.636166670000001</v>
-      </c>
-      <c r="F5">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>387.86584470000003</v>
-      </c>
-      <c r="H5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5">
-        <v>54584.28</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>70</v>
-      </c>
-      <c r="L5" t="s">
-        <v>71</v>
-      </c>
-      <c r="M5">
-        <v>3.3342933166140003E-2</v>
-      </c>
-      <c r="N5">
-        <v>1.7770684161179998E-2</v>
-      </c>
-      <c r="O5">
-        <v>0.46203778819067998</v>
-      </c>
-      <c r="P5">
-        <v>17</v>
-      </c>
-      <c r="Q5">
-        <v>0.97955493000000005</v>
-      </c>
-      <c r="R5">
-        <v>1.10870807</v>
-      </c>
-      <c r="S5" s="1">
-        <v>0.21855670106299999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6">
-        <v>-4.9944166670000003</v>
-      </c>
-      <c r="E6">
-        <v>43.636749999999999</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>387.86584470000003</v>
-      </c>
-      <c r="H6" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6">
-        <v>55000.5</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L6" t="s">
-        <v>71</v>
-      </c>
-      <c r="M6">
-        <v>4.49995909115E-2</v>
-      </c>
-      <c r="N6">
-        <v>2.6708848100990001E-2</v>
-      </c>
-      <c r="O6">
-        <v>0.66953936781400003</v>
-      </c>
-      <c r="P6">
+      <c r="Q8"/>
+      <c r="R8"/>
+      <c r="S8" t="n">
+        <v>0.829912023447641</v>
+      </c>
+      <c r="T8" t="n">
+        <v>52998.68</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.10460637887568</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.1222483276924</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.90858807</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.82977708</v>
+      </c>
+      <c r="Y8"/>
+      <c r="Z8"/>
+      <c r="AA8" t="n">
+        <v>0.149199979434925</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-4.99625</v>
+      </c>
+      <c r="F9" t="n">
+        <v>43.63716667</v>
+      </c>
+      <c r="G9" t="s">
+        <v>121</v>
+      </c>
+      <c r="H9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I9" t="s">
+        <v>123</v>
+      </c>
+      <c r="J9"/>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>124</v>
+      </c>
+      <c r="M9" t="s">
+        <v>125</v>
+      </c>
+      <c r="N9"/>
+      <c r="O9" t="n">
+        <v>2.38158227333922</v>
+      </c>
+      <c r="P9" t="n">
         <v>16</v>
       </c>
-      <c r="Q6">
-        <v>0.81638036999999997</v>
-      </c>
-      <c r="R6">
-        <v>0.91049316000000002</v>
-      </c>
-      <c r="S6" s="1">
-        <v>0.49965963241167799</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D7">
-        <v>-4.9903333329999997</v>
-      </c>
-      <c r="E7">
-        <v>43.637333329999997</v>
-      </c>
-      <c r="F7">
-        <v>9</v>
-      </c>
-      <c r="G7">
-        <v>406.59704590000001</v>
-      </c>
-      <c r="H7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I7">
-        <v>54742.84</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>70</v>
-      </c>
-      <c r="L7" t="s">
-        <v>71</v>
-      </c>
-      <c r="M7">
-        <v>1.8413366934239998E-2</v>
-      </c>
-      <c r="N7">
-        <v>5.8637805419010001E-2</v>
-      </c>
-      <c r="O7">
-        <v>0.70365366502811999</v>
-      </c>
-      <c r="P7">
-        <v>9</v>
-      </c>
-      <c r="Q7">
-        <v>0.45759724000000002</v>
-      </c>
-      <c r="R7">
-        <v>0.39180367999999999</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0.79376947041934198</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8">
-        <v>-4.9935833330000001</v>
-      </c>
-      <c r="E8">
-        <v>43.637</v>
-      </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>387.86584470000003</v>
-      </c>
-      <c r="H8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8">
-        <v>52998.68</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8" t="s">
-        <v>70</v>
-      </c>
-      <c r="L8" t="s">
-        <v>71</v>
-      </c>
-      <c r="M8">
-        <v>0.10460637887568</v>
-      </c>
-      <c r="N8">
-        <v>0.1222483276924</v>
-      </c>
-      <c r="O8">
-        <v>4.0908566023993798</v>
-      </c>
-      <c r="P8">
-        <v>21</v>
-      </c>
-      <c r="Q8">
-        <v>0.90858806999999997</v>
-      </c>
-      <c r="R8">
-        <v>0.82977707999999994</v>
-      </c>
-      <c r="S8" s="1">
-        <v>0.82991202344764103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9">
-        <v>-4.9962499999999999</v>
-      </c>
-      <c r="E9">
-        <v>43.637166669999999</v>
-      </c>
-      <c r="F9">
-        <v>9</v>
-      </c>
-      <c r="G9">
-        <v>387.86584470000003</v>
-      </c>
-      <c r="H9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9">
+      <c r="Q9"/>
+      <c r="R9"/>
+      <c r="S9" t="n">
+        <v>0.610225303278208</v>
+      </c>
+      <c r="T9" t="n">
         <v>50877.94</v>
       </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>70</v>
-      </c>
-      <c r="L9" t="s">
-        <v>71</v>
-      </c>
-      <c r="M9">
-        <v>0.15478221013457999</v>
-      </c>
-      <c r="N9">
-        <v>0.11340867968281999</v>
-      </c>
-      <c r="O9">
-        <v>2.38158227333922</v>
-      </c>
-      <c r="P9">
-        <v>16</v>
-      </c>
-      <c r="Q9">
-        <v>0.54486730999999999</v>
-      </c>
-      <c r="R9">
-        <v>0.63220602000000004</v>
-      </c>
-      <c r="S9" s="1">
-        <v>0.61022530327820801</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U9" t="n">
+        <v>0.15478221013458</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.11340867968282</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.54486731</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.63220602</v>
+      </c>
+      <c r="Y9"/>
+      <c r="Z9"/>
+      <c r="AA9" t="n">
+        <v>0.228105141522372</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>149</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10">
-        <v>-4.9974999999999996</v>
-      </c>
-      <c r="E10">
-        <v>43.636833330000002</v>
-      </c>
-      <c r="F10">
-        <v>9</v>
-      </c>
-      <c r="G10">
-        <v>387.86584470000003</v>
+        <v>119</v>
+      </c>
+      <c r="D10" t="s">
+        <v>151</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-4.9975</v>
+      </c>
+      <c r="F10" t="n">
+        <v>43.63683333</v>
+      </c>
+      <c r="G10" t="s">
+        <v>121</v>
       </c>
       <c r="H10" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10">
+        <v>122</v>
+      </c>
+      <c r="I10" t="s">
+        <v>123</v>
+      </c>
+      <c r="J10"/>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
+        <v>124</v>
+      </c>
+      <c r="M10" t="s">
+        <v>125</v>
+      </c>
+      <c r="N10"/>
+      <c r="O10" t="n">
+        <v>0.62975454896319</v>
+      </c>
+      <c r="P10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q10"/>
+      <c r="R10"/>
+      <c r="S10" t="n">
+        <v>0.718309859173627</v>
+      </c>
+      <c r="T10" t="n">
         <v>52086.96</v>
       </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10" t="s">
-        <v>70</v>
-      </c>
-      <c r="L10" t="s">
-        <v>71</v>
-      </c>
-      <c r="M10">
-        <v>1.3304673569459999E-2</v>
-      </c>
-      <c r="N10">
-        <v>2.9988311855389999E-2</v>
-      </c>
-      <c r="O10">
-        <v>0.62975454896319005</v>
-      </c>
-      <c r="P10">
-        <v>15</v>
-      </c>
-      <c r="Q10">
-        <v>1.1844879800000001</v>
-      </c>
-      <c r="R10">
-        <v>0.82085432000000003</v>
-      </c>
-      <c r="S10" s="1">
-        <v>0.718309859173627</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U10" t="n">
+        <v>0.01330467356946</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.02998831185539</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.18448798</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.82085432</v>
+      </c>
+      <c r="Y10"/>
+      <c r="Z10"/>
+      <c r="AA10" t="n">
+        <v>0.246798975642397</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>153</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11">
-        <v>-4.9886666670000004</v>
-      </c>
-      <c r="E11">
-        <v>43.637333329999997</v>
-      </c>
-      <c r="F11">
-        <v>9</v>
-      </c>
-      <c r="G11">
-        <v>406.59704590000001</v>
+        <v>119</v>
+      </c>
+      <c r="D11" t="s">
+        <v>154</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-4.988666667</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.63733333</v>
+      </c>
+      <c r="G11" t="s">
+        <v>121</v>
       </c>
       <c r="H11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I11">
+        <v>142</v>
+      </c>
+      <c r="I11" t="s">
+        <v>123</v>
+      </c>
+      <c r="J11"/>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="s">
+        <v>124</v>
+      </c>
+      <c r="M11" t="s">
+        <v>125</v>
+      </c>
+      <c r="N11"/>
+      <c r="O11" t="n">
+        <v>4.8100015003913</v>
+      </c>
+      <c r="P11" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q11"/>
+      <c r="R11"/>
+      <c r="S11" t="n">
+        <v>0.401418260116867</v>
+      </c>
+      <c r="T11" t="n">
         <v>51591.46</v>
       </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L11" t="s">
-        <v>71</v>
-      </c>
-      <c r="M11">
+      <c r="U11" t="n">
         <v>0.10635481142071</v>
       </c>
-      <c r="N11">
-        <v>0.15306796900530001</v>
-      </c>
-      <c r="O11">
-        <v>4.8100015003912997</v>
-      </c>
-      <c r="P11">
-        <v>18</v>
-      </c>
-      <c r="Q11">
-        <v>0.75350715999999995</v>
-      </c>
-      <c r="R11">
-        <v>0.67379054999999999</v>
-      </c>
-      <c r="S11" s="1">
-        <v>0.40141826011686699</v>
+      <c r="V11" t="n">
+        <v>0.1530679690053</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.75350716</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.67379055</v>
+      </c>
+      <c r="Y11"/>
+      <c r="Z11"/>
+      <c r="AA11" t="n">
+        <v>0.398590181909455</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -7000,13 +7317,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{900C0744-D61E-4C85-80CF-85BD55643319}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB320583-3C28-43A9-8679-32E11E447C7F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEE87A98-17C4-4FE8-922A-A4DA60A14FC7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{194C2DF4-AF08-4817-96CA-4789798F9D14}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B3E2826-8366-4516-851C-B5F7A234537A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9CE8F9A-A39C-439E-B01A-5753C6BDA317}"/>
 </file>